--- a/template/Standard_Quote_Template.xlsx
+++ b/template/Standard_Quote_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NC566\Desktop\가온아이\업무 서류(견적, 계약 등)\사이트별 서류\유한양행\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisob/Desktop/project2/AutoPO_Project/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF48F246-062F-405E-A400-2667F0BCBBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3509FED-DBF1-7E41-9BA7-9C965ECBAB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15840" xr2:uid="{2312F278-35BD-43B6-8969-4121AAB0341E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{2312F278-35BD-43B6-8969-4121AAB0341E}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="9" r:id="rId1"/>
@@ -51,6 +51,30 @@
     <definedName name="_SMART_SCSIarray">[2]Supplement2!#REF!</definedName>
     <definedName name="_SRP1">#REF!</definedName>
     <definedName name="_US1">#REF!</definedName>
+    <definedName name="가" localSheetId="0">#REF!</definedName>
+    <definedName name="가">#REF!</definedName>
+    <definedName name="게르" localSheetId="0">#REF!</definedName>
+    <definedName name="게르">#REF!</definedName>
+    <definedName name="게르마니12" localSheetId="0">#REF!</definedName>
+    <definedName name="게르마니12">#REF!</definedName>
+    <definedName name="기준단가표">[7]기준단가표!$A$3:$G$24</definedName>
+    <definedName name="기준데이타" localSheetId="0">#REF!</definedName>
+    <definedName name="기준데이타">#REF!</definedName>
+    <definedName name="대양12" localSheetId="0">#REF!</definedName>
+    <definedName name="대양12">#REF!</definedName>
+    <definedName name="대양전기" localSheetId="0">#REF!</definedName>
+    <definedName name="대양전기">#REF!</definedName>
+    <definedName name="대양전기12" localSheetId="0">#REF!</definedName>
+    <definedName name="대양전기12">#REF!</definedName>
+    <definedName name="대양전기123" localSheetId="0">#REF!</definedName>
+    <definedName name="대양전기123">#REF!</definedName>
+    <definedName name="성창">#REF!</definedName>
+    <definedName name="성창09.06">#REF!</definedName>
+    <definedName name="정일" localSheetId="0">#REF!</definedName>
+    <definedName name="정일">#REF!</definedName>
+    <definedName name="제_품_명">견적서!#REF!</definedName>
+    <definedName name="ㅣ라" localSheetId="0">#REF!</definedName>
+    <definedName name="ㅣ라">#REF!</definedName>
     <definedName name="Chart_1">"Chart 1"</definedName>
     <definedName name="cost">#REF!</definedName>
     <definedName name="DazzlerPCI_array" localSheetId="0">[1]Supplement2!#REF!</definedName>
@@ -76,30 +100,6 @@
     <definedName name="TStorm_M2_Processor" localSheetId="0">[1]Supplement2!#REF!</definedName>
     <definedName name="TStorm_M2_Processor">[2]Supplement2!#REF!</definedName>
     <definedName name="UPG_PN">#REF!</definedName>
-    <definedName name="가" localSheetId="0">#REF!</definedName>
-    <definedName name="가">#REF!</definedName>
-    <definedName name="게르" localSheetId="0">#REF!</definedName>
-    <definedName name="게르">#REF!</definedName>
-    <definedName name="게르마니12" localSheetId="0">#REF!</definedName>
-    <definedName name="게르마니12">#REF!</definedName>
-    <definedName name="기준단가표">[7]기준단가표!$A$3:$G$24</definedName>
-    <definedName name="기준데이타" localSheetId="0">#REF!</definedName>
-    <definedName name="기준데이타">#REF!</definedName>
-    <definedName name="대양12" localSheetId="0">#REF!</definedName>
-    <definedName name="대양12">#REF!</definedName>
-    <definedName name="대양전기" localSheetId="0">#REF!</definedName>
-    <definedName name="대양전기">#REF!</definedName>
-    <definedName name="대양전기12" localSheetId="0">#REF!</definedName>
-    <definedName name="대양전기12">#REF!</definedName>
-    <definedName name="대양전기123" localSheetId="0">#REF!</definedName>
-    <definedName name="대양전기123">#REF!</definedName>
-    <definedName name="성창">#REF!</definedName>
-    <definedName name="성창09.06">#REF!</definedName>
-    <definedName name="정일" localSheetId="0">#REF!</definedName>
-    <definedName name="정일">#REF!</definedName>
-    <definedName name="제_품_명">견적서!#REF!</definedName>
-    <definedName name="ㅣ라" localSheetId="0">#REF!</definedName>
-    <definedName name="ㅣ라">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -669,13 +669,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="177" formatCode="&quot;견적금액 : &quot;#,##0&quot;,000원 (VAT별도)&quot;;&quot;견적금액: &quot;\-#,##0,000&quot;원(VAT별도)&quot;"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="179" formatCode="&quot;견적금액 : &quot;#,##0&quot;,000원 (VAT별도)&quot;;&quot;견적금액: &quot;\-#,##0,000&quot;원(VAT별도)&quot;"/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="181" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="182" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -1798,7 +1798,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1812,10 +1812,10 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1841,7 +1841,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1856,13 +1856,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1871,7 +1871,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1880,7 +1880,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1895,13 +1895,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="18" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1910,7 +1910,7 @@
     <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1919,7 +1919,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1935,13 +1935,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
@@ -1950,13 +1950,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1980,10 +1980,10 @@
     <xf numFmtId="9" fontId="21" fillId="0" borderId="51" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="52" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="52" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1995,31 +1995,31 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="4" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="4" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="4" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="4" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="4" borderId="56" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="4" borderId="56" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2028,22 +2028,22 @@
     <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="6" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="6" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
@@ -2058,7 +2058,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2076,70 +2076,64 @@
     <xf numFmtId="38" fontId="22" fillId="7" borderId="20" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="22" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="22" fillId="7" borderId="21" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="5" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="61" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="44" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2202,62 +2196,68 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="61" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="54" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="44" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -3375,912 +3375,912 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.796875" style="74" customWidth="1"/>
-    <col min="2" max="2" width="5.796875" style="79" customWidth="1"/>
-    <col min="3" max="3" width="8.796875" style="79" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" style="74" customWidth="1"/>
+    <col min="2" max="2" width="5.83203125" style="79" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="79" customWidth="1"/>
     <col min="4" max="4" width="26" style="74" customWidth="1"/>
     <col min="5" max="5" width="12.5" style="74" customWidth="1"/>
-    <col min="6" max="6" width="7.296875" style="74" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" style="77" customWidth="1"/>
-    <col min="8" max="8" width="12.296875" style="77" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="74" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="77" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="77" customWidth="1"/>
     <col min="9" max="9" width="15.5" style="77" customWidth="1"/>
-    <col min="10" max="10" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.19921875" style="74" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" style="74" customWidth="1"/>
     <col min="12" max="12" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="11.19921875" style="78" customWidth="1"/>
-    <col min="19" max="256" width="11.19921875" style="74"/>
-    <col min="257" max="257" width="3.796875" style="74" customWidth="1"/>
-    <col min="258" max="258" width="5.796875" style="74" customWidth="1"/>
-    <col min="259" max="259" width="8.796875" style="74" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="11.1640625" style="78" customWidth="1"/>
+    <col min="19" max="256" width="11.1640625" style="74"/>
+    <col min="257" max="257" width="3.83203125" style="74" customWidth="1"/>
+    <col min="258" max="258" width="5.83203125" style="74" customWidth="1"/>
+    <col min="259" max="259" width="8.83203125" style="74" customWidth="1"/>
     <col min="260" max="260" width="26" style="74" customWidth="1"/>
     <col min="261" max="261" width="12.5" style="74" customWidth="1"/>
-    <col min="262" max="262" width="7.296875" style="74" customWidth="1"/>
-    <col min="263" max="263" width="13.296875" style="74" customWidth="1"/>
-    <col min="264" max="264" width="12.296875" style="74" customWidth="1"/>
+    <col min="262" max="262" width="7.33203125" style="74" customWidth="1"/>
+    <col min="263" max="263" width="13.33203125" style="74" customWidth="1"/>
+    <col min="264" max="264" width="12.33203125" style="74" customWidth="1"/>
     <col min="265" max="265" width="15.5" style="74" customWidth="1"/>
-    <col min="266" max="266" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="267" max="267" width="11.19921875" style="74"/>
+    <col min="266" max="266" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="267" max="267" width="11.1640625" style="74"/>
     <col min="268" max="268" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="269" max="269" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="270" max="512" width="11.19921875" style="74"/>
-    <col min="513" max="513" width="3.796875" style="74" customWidth="1"/>
-    <col min="514" max="514" width="5.796875" style="74" customWidth="1"/>
-    <col min="515" max="515" width="8.796875" style="74" customWidth="1"/>
+    <col min="269" max="269" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="270" max="512" width="11.1640625" style="74"/>
+    <col min="513" max="513" width="3.83203125" style="74" customWidth="1"/>
+    <col min="514" max="514" width="5.83203125" style="74" customWidth="1"/>
+    <col min="515" max="515" width="8.83203125" style="74" customWidth="1"/>
     <col min="516" max="516" width="26" style="74" customWidth="1"/>
     <col min="517" max="517" width="12.5" style="74" customWidth="1"/>
-    <col min="518" max="518" width="7.296875" style="74" customWidth="1"/>
-    <col min="519" max="519" width="13.296875" style="74" customWidth="1"/>
-    <col min="520" max="520" width="12.296875" style="74" customWidth="1"/>
+    <col min="518" max="518" width="7.33203125" style="74" customWidth="1"/>
+    <col min="519" max="519" width="13.33203125" style="74" customWidth="1"/>
+    <col min="520" max="520" width="12.33203125" style="74" customWidth="1"/>
     <col min="521" max="521" width="15.5" style="74" customWidth="1"/>
-    <col min="522" max="522" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="523" max="523" width="11.19921875" style="74"/>
+    <col min="522" max="522" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="523" max="523" width="11.1640625" style="74"/>
     <col min="524" max="524" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="525" max="525" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="526" max="768" width="11.19921875" style="74"/>
-    <col min="769" max="769" width="3.796875" style="74" customWidth="1"/>
-    <col min="770" max="770" width="5.796875" style="74" customWidth="1"/>
-    <col min="771" max="771" width="8.796875" style="74" customWidth="1"/>
+    <col min="525" max="525" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="526" max="768" width="11.1640625" style="74"/>
+    <col min="769" max="769" width="3.83203125" style="74" customWidth="1"/>
+    <col min="770" max="770" width="5.83203125" style="74" customWidth="1"/>
+    <col min="771" max="771" width="8.83203125" style="74" customWidth="1"/>
     <col min="772" max="772" width="26" style="74" customWidth="1"/>
     <col min="773" max="773" width="12.5" style="74" customWidth="1"/>
-    <col min="774" max="774" width="7.296875" style="74" customWidth="1"/>
-    <col min="775" max="775" width="13.296875" style="74" customWidth="1"/>
-    <col min="776" max="776" width="12.296875" style="74" customWidth="1"/>
+    <col min="774" max="774" width="7.33203125" style="74" customWidth="1"/>
+    <col min="775" max="775" width="13.33203125" style="74" customWidth="1"/>
+    <col min="776" max="776" width="12.33203125" style="74" customWidth="1"/>
     <col min="777" max="777" width="15.5" style="74" customWidth="1"/>
-    <col min="778" max="778" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="779" max="779" width="11.19921875" style="74"/>
+    <col min="778" max="778" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="779" max="779" width="11.1640625" style="74"/>
     <col min="780" max="780" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="781" max="781" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="782" max="1024" width="11.19921875" style="74"/>
-    <col min="1025" max="1025" width="3.796875" style="74" customWidth="1"/>
-    <col min="1026" max="1026" width="5.796875" style="74" customWidth="1"/>
-    <col min="1027" max="1027" width="8.796875" style="74" customWidth="1"/>
+    <col min="781" max="781" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="782" max="1024" width="11.1640625" style="74"/>
+    <col min="1025" max="1025" width="3.83203125" style="74" customWidth="1"/>
+    <col min="1026" max="1026" width="5.83203125" style="74" customWidth="1"/>
+    <col min="1027" max="1027" width="8.83203125" style="74" customWidth="1"/>
     <col min="1028" max="1028" width="26" style="74" customWidth="1"/>
     <col min="1029" max="1029" width="12.5" style="74" customWidth="1"/>
-    <col min="1030" max="1030" width="7.296875" style="74" customWidth="1"/>
-    <col min="1031" max="1031" width="13.296875" style="74" customWidth="1"/>
-    <col min="1032" max="1032" width="12.296875" style="74" customWidth="1"/>
+    <col min="1030" max="1030" width="7.33203125" style="74" customWidth="1"/>
+    <col min="1031" max="1031" width="13.33203125" style="74" customWidth="1"/>
+    <col min="1032" max="1032" width="12.33203125" style="74" customWidth="1"/>
     <col min="1033" max="1033" width="15.5" style="74" customWidth="1"/>
-    <col min="1034" max="1034" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="1035" max="1035" width="11.19921875" style="74"/>
+    <col min="1034" max="1034" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="1035" max="1035" width="11.1640625" style="74"/>
     <col min="1036" max="1036" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="1037" max="1037" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="1038" max="1280" width="11.19921875" style="74"/>
-    <col min="1281" max="1281" width="3.796875" style="74" customWidth="1"/>
-    <col min="1282" max="1282" width="5.796875" style="74" customWidth="1"/>
-    <col min="1283" max="1283" width="8.796875" style="74" customWidth="1"/>
+    <col min="1037" max="1037" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="1038" max="1280" width="11.1640625" style="74"/>
+    <col min="1281" max="1281" width="3.83203125" style="74" customWidth="1"/>
+    <col min="1282" max="1282" width="5.83203125" style="74" customWidth="1"/>
+    <col min="1283" max="1283" width="8.83203125" style="74" customWidth="1"/>
     <col min="1284" max="1284" width="26" style="74" customWidth="1"/>
     <col min="1285" max="1285" width="12.5" style="74" customWidth="1"/>
-    <col min="1286" max="1286" width="7.296875" style="74" customWidth="1"/>
-    <col min="1287" max="1287" width="13.296875" style="74" customWidth="1"/>
-    <col min="1288" max="1288" width="12.296875" style="74" customWidth="1"/>
+    <col min="1286" max="1286" width="7.33203125" style="74" customWidth="1"/>
+    <col min="1287" max="1287" width="13.33203125" style="74" customWidth="1"/>
+    <col min="1288" max="1288" width="12.33203125" style="74" customWidth="1"/>
     <col min="1289" max="1289" width="15.5" style="74" customWidth="1"/>
-    <col min="1290" max="1290" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="1291" max="1291" width="11.19921875" style="74"/>
+    <col min="1290" max="1290" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="1291" max="1291" width="11.1640625" style="74"/>
     <col min="1292" max="1292" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="1293" max="1293" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="1294" max="1536" width="11.19921875" style="74"/>
-    <col min="1537" max="1537" width="3.796875" style="74" customWidth="1"/>
-    <col min="1538" max="1538" width="5.796875" style="74" customWidth="1"/>
-    <col min="1539" max="1539" width="8.796875" style="74" customWidth="1"/>
+    <col min="1293" max="1293" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="1294" max="1536" width="11.1640625" style="74"/>
+    <col min="1537" max="1537" width="3.83203125" style="74" customWidth="1"/>
+    <col min="1538" max="1538" width="5.83203125" style="74" customWidth="1"/>
+    <col min="1539" max="1539" width="8.83203125" style="74" customWidth="1"/>
     <col min="1540" max="1540" width="26" style="74" customWidth="1"/>
     <col min="1541" max="1541" width="12.5" style="74" customWidth="1"/>
-    <col min="1542" max="1542" width="7.296875" style="74" customWidth="1"/>
-    <col min="1543" max="1543" width="13.296875" style="74" customWidth="1"/>
-    <col min="1544" max="1544" width="12.296875" style="74" customWidth="1"/>
+    <col min="1542" max="1542" width="7.33203125" style="74" customWidth="1"/>
+    <col min="1543" max="1543" width="13.33203125" style="74" customWidth="1"/>
+    <col min="1544" max="1544" width="12.33203125" style="74" customWidth="1"/>
     <col min="1545" max="1545" width="15.5" style="74" customWidth="1"/>
-    <col min="1546" max="1546" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="1547" max="1547" width="11.19921875" style="74"/>
+    <col min="1546" max="1546" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="1547" max="1547" width="11.1640625" style="74"/>
     <col min="1548" max="1548" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="1549" max="1549" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="1550" max="1792" width="11.19921875" style="74"/>
-    <col min="1793" max="1793" width="3.796875" style="74" customWidth="1"/>
-    <col min="1794" max="1794" width="5.796875" style="74" customWidth="1"/>
-    <col min="1795" max="1795" width="8.796875" style="74" customWidth="1"/>
+    <col min="1549" max="1549" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="1550" max="1792" width="11.1640625" style="74"/>
+    <col min="1793" max="1793" width="3.83203125" style="74" customWidth="1"/>
+    <col min="1794" max="1794" width="5.83203125" style="74" customWidth="1"/>
+    <col min="1795" max="1795" width="8.83203125" style="74" customWidth="1"/>
     <col min="1796" max="1796" width="26" style="74" customWidth="1"/>
     <col min="1797" max="1797" width="12.5" style="74" customWidth="1"/>
-    <col min="1798" max="1798" width="7.296875" style="74" customWidth="1"/>
-    <col min="1799" max="1799" width="13.296875" style="74" customWidth="1"/>
-    <col min="1800" max="1800" width="12.296875" style="74" customWidth="1"/>
+    <col min="1798" max="1798" width="7.33203125" style="74" customWidth="1"/>
+    <col min="1799" max="1799" width="13.33203125" style="74" customWidth="1"/>
+    <col min="1800" max="1800" width="12.33203125" style="74" customWidth="1"/>
     <col min="1801" max="1801" width="15.5" style="74" customWidth="1"/>
-    <col min="1802" max="1802" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="1803" max="1803" width="11.19921875" style="74"/>
+    <col min="1802" max="1802" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="1803" max="1803" width="11.1640625" style="74"/>
     <col min="1804" max="1804" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="1805" max="1805" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="1806" max="2048" width="11.19921875" style="74"/>
-    <col min="2049" max="2049" width="3.796875" style="74" customWidth="1"/>
-    <col min="2050" max="2050" width="5.796875" style="74" customWidth="1"/>
-    <col min="2051" max="2051" width="8.796875" style="74" customWidth="1"/>
+    <col min="1805" max="1805" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="1806" max="2048" width="11.1640625" style="74"/>
+    <col min="2049" max="2049" width="3.83203125" style="74" customWidth="1"/>
+    <col min="2050" max="2050" width="5.83203125" style="74" customWidth="1"/>
+    <col min="2051" max="2051" width="8.83203125" style="74" customWidth="1"/>
     <col min="2052" max="2052" width="26" style="74" customWidth="1"/>
     <col min="2053" max="2053" width="12.5" style="74" customWidth="1"/>
-    <col min="2054" max="2054" width="7.296875" style="74" customWidth="1"/>
-    <col min="2055" max="2055" width="13.296875" style="74" customWidth="1"/>
-    <col min="2056" max="2056" width="12.296875" style="74" customWidth="1"/>
+    <col min="2054" max="2054" width="7.33203125" style="74" customWidth="1"/>
+    <col min="2055" max="2055" width="13.33203125" style="74" customWidth="1"/>
+    <col min="2056" max="2056" width="12.33203125" style="74" customWidth="1"/>
     <col min="2057" max="2057" width="15.5" style="74" customWidth="1"/>
-    <col min="2058" max="2058" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="2059" max="2059" width="11.19921875" style="74"/>
+    <col min="2058" max="2058" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="2059" max="2059" width="11.1640625" style="74"/>
     <col min="2060" max="2060" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="2061" max="2061" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="2062" max="2304" width="11.19921875" style="74"/>
-    <col min="2305" max="2305" width="3.796875" style="74" customWidth="1"/>
-    <col min="2306" max="2306" width="5.796875" style="74" customWidth="1"/>
-    <col min="2307" max="2307" width="8.796875" style="74" customWidth="1"/>
+    <col min="2061" max="2061" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="2062" max="2304" width="11.1640625" style="74"/>
+    <col min="2305" max="2305" width="3.83203125" style="74" customWidth="1"/>
+    <col min="2306" max="2306" width="5.83203125" style="74" customWidth="1"/>
+    <col min="2307" max="2307" width="8.83203125" style="74" customWidth="1"/>
     <col min="2308" max="2308" width="26" style="74" customWidth="1"/>
     <col min="2309" max="2309" width="12.5" style="74" customWidth="1"/>
-    <col min="2310" max="2310" width="7.296875" style="74" customWidth="1"/>
-    <col min="2311" max="2311" width="13.296875" style="74" customWidth="1"/>
-    <col min="2312" max="2312" width="12.296875" style="74" customWidth="1"/>
+    <col min="2310" max="2310" width="7.33203125" style="74" customWidth="1"/>
+    <col min="2311" max="2311" width="13.33203125" style="74" customWidth="1"/>
+    <col min="2312" max="2312" width="12.33203125" style="74" customWidth="1"/>
     <col min="2313" max="2313" width="15.5" style="74" customWidth="1"/>
-    <col min="2314" max="2314" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="2315" max="2315" width="11.19921875" style="74"/>
+    <col min="2314" max="2314" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="2315" max="2315" width="11.1640625" style="74"/>
     <col min="2316" max="2316" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="2317" max="2317" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="2318" max="2560" width="11.19921875" style="74"/>
-    <col min="2561" max="2561" width="3.796875" style="74" customWidth="1"/>
-    <col min="2562" max="2562" width="5.796875" style="74" customWidth="1"/>
-    <col min="2563" max="2563" width="8.796875" style="74" customWidth="1"/>
+    <col min="2317" max="2317" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="2318" max="2560" width="11.1640625" style="74"/>
+    <col min="2561" max="2561" width="3.83203125" style="74" customWidth="1"/>
+    <col min="2562" max="2562" width="5.83203125" style="74" customWidth="1"/>
+    <col min="2563" max="2563" width="8.83203125" style="74" customWidth="1"/>
     <col min="2564" max="2564" width="26" style="74" customWidth="1"/>
     <col min="2565" max="2565" width="12.5" style="74" customWidth="1"/>
-    <col min="2566" max="2566" width="7.296875" style="74" customWidth="1"/>
-    <col min="2567" max="2567" width="13.296875" style="74" customWidth="1"/>
-    <col min="2568" max="2568" width="12.296875" style="74" customWidth="1"/>
+    <col min="2566" max="2566" width="7.33203125" style="74" customWidth="1"/>
+    <col min="2567" max="2567" width="13.33203125" style="74" customWidth="1"/>
+    <col min="2568" max="2568" width="12.33203125" style="74" customWidth="1"/>
     <col min="2569" max="2569" width="15.5" style="74" customWidth="1"/>
-    <col min="2570" max="2570" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="2571" max="2571" width="11.19921875" style="74"/>
+    <col min="2570" max="2570" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="2571" max="2571" width="11.1640625" style="74"/>
     <col min="2572" max="2572" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="2573" max="2573" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="2574" max="2816" width="11.19921875" style="74"/>
-    <col min="2817" max="2817" width="3.796875" style="74" customWidth="1"/>
-    <col min="2818" max="2818" width="5.796875" style="74" customWidth="1"/>
-    <col min="2819" max="2819" width="8.796875" style="74" customWidth="1"/>
+    <col min="2573" max="2573" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="2574" max="2816" width="11.1640625" style="74"/>
+    <col min="2817" max="2817" width="3.83203125" style="74" customWidth="1"/>
+    <col min="2818" max="2818" width="5.83203125" style="74" customWidth="1"/>
+    <col min="2819" max="2819" width="8.83203125" style="74" customWidth="1"/>
     <col min="2820" max="2820" width="26" style="74" customWidth="1"/>
     <col min="2821" max="2821" width="12.5" style="74" customWidth="1"/>
-    <col min="2822" max="2822" width="7.296875" style="74" customWidth="1"/>
-    <col min="2823" max="2823" width="13.296875" style="74" customWidth="1"/>
-    <col min="2824" max="2824" width="12.296875" style="74" customWidth="1"/>
+    <col min="2822" max="2822" width="7.33203125" style="74" customWidth="1"/>
+    <col min="2823" max="2823" width="13.33203125" style="74" customWidth="1"/>
+    <col min="2824" max="2824" width="12.33203125" style="74" customWidth="1"/>
     <col min="2825" max="2825" width="15.5" style="74" customWidth="1"/>
-    <col min="2826" max="2826" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="2827" max="2827" width="11.19921875" style="74"/>
+    <col min="2826" max="2826" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="2827" max="2827" width="11.1640625" style="74"/>
     <col min="2828" max="2828" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="2829" max="2829" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="2830" max="3072" width="11.19921875" style="74"/>
-    <col min="3073" max="3073" width="3.796875" style="74" customWidth="1"/>
-    <col min="3074" max="3074" width="5.796875" style="74" customWidth="1"/>
-    <col min="3075" max="3075" width="8.796875" style="74" customWidth="1"/>
+    <col min="2829" max="2829" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="2830" max="3072" width="11.1640625" style="74"/>
+    <col min="3073" max="3073" width="3.83203125" style="74" customWidth="1"/>
+    <col min="3074" max="3074" width="5.83203125" style="74" customWidth="1"/>
+    <col min="3075" max="3075" width="8.83203125" style="74" customWidth="1"/>
     <col min="3076" max="3076" width="26" style="74" customWidth="1"/>
     <col min="3077" max="3077" width="12.5" style="74" customWidth="1"/>
-    <col min="3078" max="3078" width="7.296875" style="74" customWidth="1"/>
-    <col min="3079" max="3079" width="13.296875" style="74" customWidth="1"/>
-    <col min="3080" max="3080" width="12.296875" style="74" customWidth="1"/>
+    <col min="3078" max="3078" width="7.33203125" style="74" customWidth="1"/>
+    <col min="3079" max="3079" width="13.33203125" style="74" customWidth="1"/>
+    <col min="3080" max="3080" width="12.33203125" style="74" customWidth="1"/>
     <col min="3081" max="3081" width="15.5" style="74" customWidth="1"/>
-    <col min="3082" max="3082" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="3083" max="3083" width="11.19921875" style="74"/>
+    <col min="3082" max="3082" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="3083" max="3083" width="11.1640625" style="74"/>
     <col min="3084" max="3084" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="3085" max="3085" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="3086" max="3328" width="11.19921875" style="74"/>
-    <col min="3329" max="3329" width="3.796875" style="74" customWidth="1"/>
-    <col min="3330" max="3330" width="5.796875" style="74" customWidth="1"/>
-    <col min="3331" max="3331" width="8.796875" style="74" customWidth="1"/>
+    <col min="3085" max="3085" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="3086" max="3328" width="11.1640625" style="74"/>
+    <col min="3329" max="3329" width="3.83203125" style="74" customWidth="1"/>
+    <col min="3330" max="3330" width="5.83203125" style="74" customWidth="1"/>
+    <col min="3331" max="3331" width="8.83203125" style="74" customWidth="1"/>
     <col min="3332" max="3332" width="26" style="74" customWidth="1"/>
     <col min="3333" max="3333" width="12.5" style="74" customWidth="1"/>
-    <col min="3334" max="3334" width="7.296875" style="74" customWidth="1"/>
-    <col min="3335" max="3335" width="13.296875" style="74" customWidth="1"/>
-    <col min="3336" max="3336" width="12.296875" style="74" customWidth="1"/>
+    <col min="3334" max="3334" width="7.33203125" style="74" customWidth="1"/>
+    <col min="3335" max="3335" width="13.33203125" style="74" customWidth="1"/>
+    <col min="3336" max="3336" width="12.33203125" style="74" customWidth="1"/>
     <col min="3337" max="3337" width="15.5" style="74" customWidth="1"/>
-    <col min="3338" max="3338" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="3339" max="3339" width="11.19921875" style="74"/>
+    <col min="3338" max="3338" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="3339" max="3339" width="11.1640625" style="74"/>
     <col min="3340" max="3340" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="3341" max="3341" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="3342" max="3584" width="11.19921875" style="74"/>
-    <col min="3585" max="3585" width="3.796875" style="74" customWidth="1"/>
-    <col min="3586" max="3586" width="5.796875" style="74" customWidth="1"/>
-    <col min="3587" max="3587" width="8.796875" style="74" customWidth="1"/>
+    <col min="3341" max="3341" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="3342" max="3584" width="11.1640625" style="74"/>
+    <col min="3585" max="3585" width="3.83203125" style="74" customWidth="1"/>
+    <col min="3586" max="3586" width="5.83203125" style="74" customWidth="1"/>
+    <col min="3587" max="3587" width="8.83203125" style="74" customWidth="1"/>
     <col min="3588" max="3588" width="26" style="74" customWidth="1"/>
     <col min="3589" max="3589" width="12.5" style="74" customWidth="1"/>
-    <col min="3590" max="3590" width="7.296875" style="74" customWidth="1"/>
-    <col min="3591" max="3591" width="13.296875" style="74" customWidth="1"/>
-    <col min="3592" max="3592" width="12.296875" style="74" customWidth="1"/>
+    <col min="3590" max="3590" width="7.33203125" style="74" customWidth="1"/>
+    <col min="3591" max="3591" width="13.33203125" style="74" customWidth="1"/>
+    <col min="3592" max="3592" width="12.33203125" style="74" customWidth="1"/>
     <col min="3593" max="3593" width="15.5" style="74" customWidth="1"/>
-    <col min="3594" max="3594" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="3595" max="3595" width="11.19921875" style="74"/>
+    <col min="3594" max="3594" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="3595" max="3595" width="11.1640625" style="74"/>
     <col min="3596" max="3596" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="3597" max="3597" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="3598" max="3840" width="11.19921875" style="74"/>
-    <col min="3841" max="3841" width="3.796875" style="74" customWidth="1"/>
-    <col min="3842" max="3842" width="5.796875" style="74" customWidth="1"/>
-    <col min="3843" max="3843" width="8.796875" style="74" customWidth="1"/>
+    <col min="3597" max="3597" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="3598" max="3840" width="11.1640625" style="74"/>
+    <col min="3841" max="3841" width="3.83203125" style="74" customWidth="1"/>
+    <col min="3842" max="3842" width="5.83203125" style="74" customWidth="1"/>
+    <col min="3843" max="3843" width="8.83203125" style="74" customWidth="1"/>
     <col min="3844" max="3844" width="26" style="74" customWidth="1"/>
     <col min="3845" max="3845" width="12.5" style="74" customWidth="1"/>
-    <col min="3846" max="3846" width="7.296875" style="74" customWidth="1"/>
-    <col min="3847" max="3847" width="13.296875" style="74" customWidth="1"/>
-    <col min="3848" max="3848" width="12.296875" style="74" customWidth="1"/>
+    <col min="3846" max="3846" width="7.33203125" style="74" customWidth="1"/>
+    <col min="3847" max="3847" width="13.33203125" style="74" customWidth="1"/>
+    <col min="3848" max="3848" width="12.33203125" style="74" customWidth="1"/>
     <col min="3849" max="3849" width="15.5" style="74" customWidth="1"/>
-    <col min="3850" max="3850" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="3851" max="3851" width="11.19921875" style="74"/>
+    <col min="3850" max="3850" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="3851" max="3851" width="11.1640625" style="74"/>
     <col min="3852" max="3852" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="3853" max="3853" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="3854" max="4096" width="11.19921875" style="74"/>
-    <col min="4097" max="4097" width="3.796875" style="74" customWidth="1"/>
-    <col min="4098" max="4098" width="5.796875" style="74" customWidth="1"/>
-    <col min="4099" max="4099" width="8.796875" style="74" customWidth="1"/>
+    <col min="3853" max="3853" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="3854" max="4096" width="11.1640625" style="74"/>
+    <col min="4097" max="4097" width="3.83203125" style="74" customWidth="1"/>
+    <col min="4098" max="4098" width="5.83203125" style="74" customWidth="1"/>
+    <col min="4099" max="4099" width="8.83203125" style="74" customWidth="1"/>
     <col min="4100" max="4100" width="26" style="74" customWidth="1"/>
     <col min="4101" max="4101" width="12.5" style="74" customWidth="1"/>
-    <col min="4102" max="4102" width="7.296875" style="74" customWidth="1"/>
-    <col min="4103" max="4103" width="13.296875" style="74" customWidth="1"/>
-    <col min="4104" max="4104" width="12.296875" style="74" customWidth="1"/>
+    <col min="4102" max="4102" width="7.33203125" style="74" customWidth="1"/>
+    <col min="4103" max="4103" width="13.33203125" style="74" customWidth="1"/>
+    <col min="4104" max="4104" width="12.33203125" style="74" customWidth="1"/>
     <col min="4105" max="4105" width="15.5" style="74" customWidth="1"/>
-    <col min="4106" max="4106" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="4107" max="4107" width="11.19921875" style="74"/>
+    <col min="4106" max="4106" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="4107" max="4107" width="11.1640625" style="74"/>
     <col min="4108" max="4108" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="4109" max="4109" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="4110" max="4352" width="11.19921875" style="74"/>
-    <col min="4353" max="4353" width="3.796875" style="74" customWidth="1"/>
-    <col min="4354" max="4354" width="5.796875" style="74" customWidth="1"/>
-    <col min="4355" max="4355" width="8.796875" style="74" customWidth="1"/>
+    <col min="4109" max="4109" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="4110" max="4352" width="11.1640625" style="74"/>
+    <col min="4353" max="4353" width="3.83203125" style="74" customWidth="1"/>
+    <col min="4354" max="4354" width="5.83203125" style="74" customWidth="1"/>
+    <col min="4355" max="4355" width="8.83203125" style="74" customWidth="1"/>
     <col min="4356" max="4356" width="26" style="74" customWidth="1"/>
     <col min="4357" max="4357" width="12.5" style="74" customWidth="1"/>
-    <col min="4358" max="4358" width="7.296875" style="74" customWidth="1"/>
-    <col min="4359" max="4359" width="13.296875" style="74" customWidth="1"/>
-    <col min="4360" max="4360" width="12.296875" style="74" customWidth="1"/>
+    <col min="4358" max="4358" width="7.33203125" style="74" customWidth="1"/>
+    <col min="4359" max="4359" width="13.33203125" style="74" customWidth="1"/>
+    <col min="4360" max="4360" width="12.33203125" style="74" customWidth="1"/>
     <col min="4361" max="4361" width="15.5" style="74" customWidth="1"/>
-    <col min="4362" max="4362" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="4363" max="4363" width="11.19921875" style="74"/>
+    <col min="4362" max="4362" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="4363" max="4363" width="11.1640625" style="74"/>
     <col min="4364" max="4364" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="4365" max="4365" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="4366" max="4608" width="11.19921875" style="74"/>
-    <col min="4609" max="4609" width="3.796875" style="74" customWidth="1"/>
-    <col min="4610" max="4610" width="5.796875" style="74" customWidth="1"/>
-    <col min="4611" max="4611" width="8.796875" style="74" customWidth="1"/>
+    <col min="4365" max="4365" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="4366" max="4608" width="11.1640625" style="74"/>
+    <col min="4609" max="4609" width="3.83203125" style="74" customWidth="1"/>
+    <col min="4610" max="4610" width="5.83203125" style="74" customWidth="1"/>
+    <col min="4611" max="4611" width="8.83203125" style="74" customWidth="1"/>
     <col min="4612" max="4612" width="26" style="74" customWidth="1"/>
     <col min="4613" max="4613" width="12.5" style="74" customWidth="1"/>
-    <col min="4614" max="4614" width="7.296875" style="74" customWidth="1"/>
-    <col min="4615" max="4615" width="13.296875" style="74" customWidth="1"/>
-    <col min="4616" max="4616" width="12.296875" style="74" customWidth="1"/>
+    <col min="4614" max="4614" width="7.33203125" style="74" customWidth="1"/>
+    <col min="4615" max="4615" width="13.33203125" style="74" customWidth="1"/>
+    <col min="4616" max="4616" width="12.33203125" style="74" customWidth="1"/>
     <col min="4617" max="4617" width="15.5" style="74" customWidth="1"/>
-    <col min="4618" max="4618" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="4619" max="4619" width="11.19921875" style="74"/>
+    <col min="4618" max="4618" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="4619" max="4619" width="11.1640625" style="74"/>
     <col min="4620" max="4620" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="4621" max="4621" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="4622" max="4864" width="11.19921875" style="74"/>
-    <col min="4865" max="4865" width="3.796875" style="74" customWidth="1"/>
-    <col min="4866" max="4866" width="5.796875" style="74" customWidth="1"/>
-    <col min="4867" max="4867" width="8.796875" style="74" customWidth="1"/>
+    <col min="4621" max="4621" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="4622" max="4864" width="11.1640625" style="74"/>
+    <col min="4865" max="4865" width="3.83203125" style="74" customWidth="1"/>
+    <col min="4866" max="4866" width="5.83203125" style="74" customWidth="1"/>
+    <col min="4867" max="4867" width="8.83203125" style="74" customWidth="1"/>
     <col min="4868" max="4868" width="26" style="74" customWidth="1"/>
     <col min="4869" max="4869" width="12.5" style="74" customWidth="1"/>
-    <col min="4870" max="4870" width="7.296875" style="74" customWidth="1"/>
-    <col min="4871" max="4871" width="13.296875" style="74" customWidth="1"/>
-    <col min="4872" max="4872" width="12.296875" style="74" customWidth="1"/>
+    <col min="4870" max="4870" width="7.33203125" style="74" customWidth="1"/>
+    <col min="4871" max="4871" width="13.33203125" style="74" customWidth="1"/>
+    <col min="4872" max="4872" width="12.33203125" style="74" customWidth="1"/>
     <col min="4873" max="4873" width="15.5" style="74" customWidth="1"/>
-    <col min="4874" max="4874" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="4875" max="4875" width="11.19921875" style="74"/>
+    <col min="4874" max="4874" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="4875" max="4875" width="11.1640625" style="74"/>
     <col min="4876" max="4876" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="4877" max="4877" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="4878" max="5120" width="11.19921875" style="74"/>
-    <col min="5121" max="5121" width="3.796875" style="74" customWidth="1"/>
-    <col min="5122" max="5122" width="5.796875" style="74" customWidth="1"/>
-    <col min="5123" max="5123" width="8.796875" style="74" customWidth="1"/>
+    <col min="4877" max="4877" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="4878" max="5120" width="11.1640625" style="74"/>
+    <col min="5121" max="5121" width="3.83203125" style="74" customWidth="1"/>
+    <col min="5122" max="5122" width="5.83203125" style="74" customWidth="1"/>
+    <col min="5123" max="5123" width="8.83203125" style="74" customWidth="1"/>
     <col min="5124" max="5124" width="26" style="74" customWidth="1"/>
     <col min="5125" max="5125" width="12.5" style="74" customWidth="1"/>
-    <col min="5126" max="5126" width="7.296875" style="74" customWidth="1"/>
-    <col min="5127" max="5127" width="13.296875" style="74" customWidth="1"/>
-    <col min="5128" max="5128" width="12.296875" style="74" customWidth="1"/>
+    <col min="5126" max="5126" width="7.33203125" style="74" customWidth="1"/>
+    <col min="5127" max="5127" width="13.33203125" style="74" customWidth="1"/>
+    <col min="5128" max="5128" width="12.33203125" style="74" customWidth="1"/>
     <col min="5129" max="5129" width="15.5" style="74" customWidth="1"/>
-    <col min="5130" max="5130" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="5131" max="5131" width="11.19921875" style="74"/>
+    <col min="5130" max="5130" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5131" max="5131" width="11.1640625" style="74"/>
     <col min="5132" max="5132" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="5133" max="5133" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="5134" max="5376" width="11.19921875" style="74"/>
-    <col min="5377" max="5377" width="3.796875" style="74" customWidth="1"/>
-    <col min="5378" max="5378" width="5.796875" style="74" customWidth="1"/>
-    <col min="5379" max="5379" width="8.796875" style="74" customWidth="1"/>
+    <col min="5133" max="5133" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5134" max="5376" width="11.1640625" style="74"/>
+    <col min="5377" max="5377" width="3.83203125" style="74" customWidth="1"/>
+    <col min="5378" max="5378" width="5.83203125" style="74" customWidth="1"/>
+    <col min="5379" max="5379" width="8.83203125" style="74" customWidth="1"/>
     <col min="5380" max="5380" width="26" style="74" customWidth="1"/>
     <col min="5381" max="5381" width="12.5" style="74" customWidth="1"/>
-    <col min="5382" max="5382" width="7.296875" style="74" customWidth="1"/>
-    <col min="5383" max="5383" width="13.296875" style="74" customWidth="1"/>
-    <col min="5384" max="5384" width="12.296875" style="74" customWidth="1"/>
+    <col min="5382" max="5382" width="7.33203125" style="74" customWidth="1"/>
+    <col min="5383" max="5383" width="13.33203125" style="74" customWidth="1"/>
+    <col min="5384" max="5384" width="12.33203125" style="74" customWidth="1"/>
     <col min="5385" max="5385" width="15.5" style="74" customWidth="1"/>
-    <col min="5386" max="5386" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="5387" max="5387" width="11.19921875" style="74"/>
+    <col min="5386" max="5386" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5387" max="5387" width="11.1640625" style="74"/>
     <col min="5388" max="5388" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="5389" max="5389" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="5390" max="5632" width="11.19921875" style="74"/>
-    <col min="5633" max="5633" width="3.796875" style="74" customWidth="1"/>
-    <col min="5634" max="5634" width="5.796875" style="74" customWidth="1"/>
-    <col min="5635" max="5635" width="8.796875" style="74" customWidth="1"/>
+    <col min="5389" max="5389" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5390" max="5632" width="11.1640625" style="74"/>
+    <col min="5633" max="5633" width="3.83203125" style="74" customWidth="1"/>
+    <col min="5634" max="5634" width="5.83203125" style="74" customWidth="1"/>
+    <col min="5635" max="5635" width="8.83203125" style="74" customWidth="1"/>
     <col min="5636" max="5636" width="26" style="74" customWidth="1"/>
     <col min="5637" max="5637" width="12.5" style="74" customWidth="1"/>
-    <col min="5638" max="5638" width="7.296875" style="74" customWidth="1"/>
-    <col min="5639" max="5639" width="13.296875" style="74" customWidth="1"/>
-    <col min="5640" max="5640" width="12.296875" style="74" customWidth="1"/>
+    <col min="5638" max="5638" width="7.33203125" style="74" customWidth="1"/>
+    <col min="5639" max="5639" width="13.33203125" style="74" customWidth="1"/>
+    <col min="5640" max="5640" width="12.33203125" style="74" customWidth="1"/>
     <col min="5641" max="5641" width="15.5" style="74" customWidth="1"/>
-    <col min="5642" max="5642" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="5643" max="5643" width="11.19921875" style="74"/>
+    <col min="5642" max="5642" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5643" max="5643" width="11.1640625" style="74"/>
     <col min="5644" max="5644" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="5645" max="5645" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="5646" max="5888" width="11.19921875" style="74"/>
-    <col min="5889" max="5889" width="3.796875" style="74" customWidth="1"/>
-    <col min="5890" max="5890" width="5.796875" style="74" customWidth="1"/>
-    <col min="5891" max="5891" width="8.796875" style="74" customWidth="1"/>
+    <col min="5645" max="5645" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5646" max="5888" width="11.1640625" style="74"/>
+    <col min="5889" max="5889" width="3.83203125" style="74" customWidth="1"/>
+    <col min="5890" max="5890" width="5.83203125" style="74" customWidth="1"/>
+    <col min="5891" max="5891" width="8.83203125" style="74" customWidth="1"/>
     <col min="5892" max="5892" width="26" style="74" customWidth="1"/>
     <col min="5893" max="5893" width="12.5" style="74" customWidth="1"/>
-    <col min="5894" max="5894" width="7.296875" style="74" customWidth="1"/>
-    <col min="5895" max="5895" width="13.296875" style="74" customWidth="1"/>
-    <col min="5896" max="5896" width="12.296875" style="74" customWidth="1"/>
+    <col min="5894" max="5894" width="7.33203125" style="74" customWidth="1"/>
+    <col min="5895" max="5895" width="13.33203125" style="74" customWidth="1"/>
+    <col min="5896" max="5896" width="12.33203125" style="74" customWidth="1"/>
     <col min="5897" max="5897" width="15.5" style="74" customWidth="1"/>
-    <col min="5898" max="5898" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="5899" max="5899" width="11.19921875" style="74"/>
+    <col min="5898" max="5898" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5899" max="5899" width="11.1640625" style="74"/>
     <col min="5900" max="5900" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="5901" max="5901" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="5902" max="6144" width="11.19921875" style="74"/>
-    <col min="6145" max="6145" width="3.796875" style="74" customWidth="1"/>
-    <col min="6146" max="6146" width="5.796875" style="74" customWidth="1"/>
-    <col min="6147" max="6147" width="8.796875" style="74" customWidth="1"/>
+    <col min="5901" max="5901" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5902" max="6144" width="11.1640625" style="74"/>
+    <col min="6145" max="6145" width="3.83203125" style="74" customWidth="1"/>
+    <col min="6146" max="6146" width="5.83203125" style="74" customWidth="1"/>
+    <col min="6147" max="6147" width="8.83203125" style="74" customWidth="1"/>
     <col min="6148" max="6148" width="26" style="74" customWidth="1"/>
     <col min="6149" max="6149" width="12.5" style="74" customWidth="1"/>
-    <col min="6150" max="6150" width="7.296875" style="74" customWidth="1"/>
-    <col min="6151" max="6151" width="13.296875" style="74" customWidth="1"/>
-    <col min="6152" max="6152" width="12.296875" style="74" customWidth="1"/>
+    <col min="6150" max="6150" width="7.33203125" style="74" customWidth="1"/>
+    <col min="6151" max="6151" width="13.33203125" style="74" customWidth="1"/>
+    <col min="6152" max="6152" width="12.33203125" style="74" customWidth="1"/>
     <col min="6153" max="6153" width="15.5" style="74" customWidth="1"/>
-    <col min="6154" max="6154" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="6155" max="6155" width="11.19921875" style="74"/>
+    <col min="6154" max="6154" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="6155" max="6155" width="11.1640625" style="74"/>
     <col min="6156" max="6156" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="6157" max="6157" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="6158" max="6400" width="11.19921875" style="74"/>
-    <col min="6401" max="6401" width="3.796875" style="74" customWidth="1"/>
-    <col min="6402" max="6402" width="5.796875" style="74" customWidth="1"/>
-    <col min="6403" max="6403" width="8.796875" style="74" customWidth="1"/>
+    <col min="6157" max="6157" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="6158" max="6400" width="11.1640625" style="74"/>
+    <col min="6401" max="6401" width="3.83203125" style="74" customWidth="1"/>
+    <col min="6402" max="6402" width="5.83203125" style="74" customWidth="1"/>
+    <col min="6403" max="6403" width="8.83203125" style="74" customWidth="1"/>
     <col min="6404" max="6404" width="26" style="74" customWidth="1"/>
     <col min="6405" max="6405" width="12.5" style="74" customWidth="1"/>
-    <col min="6406" max="6406" width="7.296875" style="74" customWidth="1"/>
-    <col min="6407" max="6407" width="13.296875" style="74" customWidth="1"/>
-    <col min="6408" max="6408" width="12.296875" style="74" customWidth="1"/>
+    <col min="6406" max="6406" width="7.33203125" style="74" customWidth="1"/>
+    <col min="6407" max="6407" width="13.33203125" style="74" customWidth="1"/>
+    <col min="6408" max="6408" width="12.33203125" style="74" customWidth="1"/>
     <col min="6409" max="6409" width="15.5" style="74" customWidth="1"/>
-    <col min="6410" max="6410" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="6411" max="6411" width="11.19921875" style="74"/>
+    <col min="6410" max="6410" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="6411" max="6411" width="11.1640625" style="74"/>
     <col min="6412" max="6412" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="6413" max="6413" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="6414" max="6656" width="11.19921875" style="74"/>
-    <col min="6657" max="6657" width="3.796875" style="74" customWidth="1"/>
-    <col min="6658" max="6658" width="5.796875" style="74" customWidth="1"/>
-    <col min="6659" max="6659" width="8.796875" style="74" customWidth="1"/>
+    <col min="6413" max="6413" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="6414" max="6656" width="11.1640625" style="74"/>
+    <col min="6657" max="6657" width="3.83203125" style="74" customWidth="1"/>
+    <col min="6658" max="6658" width="5.83203125" style="74" customWidth="1"/>
+    <col min="6659" max="6659" width="8.83203125" style="74" customWidth="1"/>
     <col min="6660" max="6660" width="26" style="74" customWidth="1"/>
     <col min="6661" max="6661" width="12.5" style="74" customWidth="1"/>
-    <col min="6662" max="6662" width="7.296875" style="74" customWidth="1"/>
-    <col min="6663" max="6663" width="13.296875" style="74" customWidth="1"/>
-    <col min="6664" max="6664" width="12.296875" style="74" customWidth="1"/>
+    <col min="6662" max="6662" width="7.33203125" style="74" customWidth="1"/>
+    <col min="6663" max="6663" width="13.33203125" style="74" customWidth="1"/>
+    <col min="6664" max="6664" width="12.33203125" style="74" customWidth="1"/>
     <col min="6665" max="6665" width="15.5" style="74" customWidth="1"/>
-    <col min="6666" max="6666" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="6667" max="6667" width="11.19921875" style="74"/>
+    <col min="6666" max="6666" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="6667" max="6667" width="11.1640625" style="74"/>
     <col min="6668" max="6668" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="6669" max="6669" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="6670" max="6912" width="11.19921875" style="74"/>
-    <col min="6913" max="6913" width="3.796875" style="74" customWidth="1"/>
-    <col min="6914" max="6914" width="5.796875" style="74" customWidth="1"/>
-    <col min="6915" max="6915" width="8.796875" style="74" customWidth="1"/>
+    <col min="6669" max="6669" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="6670" max="6912" width="11.1640625" style="74"/>
+    <col min="6913" max="6913" width="3.83203125" style="74" customWidth="1"/>
+    <col min="6914" max="6914" width="5.83203125" style="74" customWidth="1"/>
+    <col min="6915" max="6915" width="8.83203125" style="74" customWidth="1"/>
     <col min="6916" max="6916" width="26" style="74" customWidth="1"/>
     <col min="6917" max="6917" width="12.5" style="74" customWidth="1"/>
-    <col min="6918" max="6918" width="7.296875" style="74" customWidth="1"/>
-    <col min="6919" max="6919" width="13.296875" style="74" customWidth="1"/>
-    <col min="6920" max="6920" width="12.296875" style="74" customWidth="1"/>
+    <col min="6918" max="6918" width="7.33203125" style="74" customWidth="1"/>
+    <col min="6919" max="6919" width="13.33203125" style="74" customWidth="1"/>
+    <col min="6920" max="6920" width="12.33203125" style="74" customWidth="1"/>
     <col min="6921" max="6921" width="15.5" style="74" customWidth="1"/>
-    <col min="6922" max="6922" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="6923" max="6923" width="11.19921875" style="74"/>
+    <col min="6922" max="6922" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="6923" max="6923" width="11.1640625" style="74"/>
     <col min="6924" max="6924" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="6925" max="6925" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="6926" max="7168" width="11.19921875" style="74"/>
-    <col min="7169" max="7169" width="3.796875" style="74" customWidth="1"/>
-    <col min="7170" max="7170" width="5.796875" style="74" customWidth="1"/>
-    <col min="7171" max="7171" width="8.796875" style="74" customWidth="1"/>
+    <col min="6925" max="6925" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="6926" max="7168" width="11.1640625" style="74"/>
+    <col min="7169" max="7169" width="3.83203125" style="74" customWidth="1"/>
+    <col min="7170" max="7170" width="5.83203125" style="74" customWidth="1"/>
+    <col min="7171" max="7171" width="8.83203125" style="74" customWidth="1"/>
     <col min="7172" max="7172" width="26" style="74" customWidth="1"/>
     <col min="7173" max="7173" width="12.5" style="74" customWidth="1"/>
-    <col min="7174" max="7174" width="7.296875" style="74" customWidth="1"/>
-    <col min="7175" max="7175" width="13.296875" style="74" customWidth="1"/>
-    <col min="7176" max="7176" width="12.296875" style="74" customWidth="1"/>
+    <col min="7174" max="7174" width="7.33203125" style="74" customWidth="1"/>
+    <col min="7175" max="7175" width="13.33203125" style="74" customWidth="1"/>
+    <col min="7176" max="7176" width="12.33203125" style="74" customWidth="1"/>
     <col min="7177" max="7177" width="15.5" style="74" customWidth="1"/>
-    <col min="7178" max="7178" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="7179" max="7179" width="11.19921875" style="74"/>
+    <col min="7178" max="7178" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="7179" max="7179" width="11.1640625" style="74"/>
     <col min="7180" max="7180" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="7181" max="7181" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="7182" max="7424" width="11.19921875" style="74"/>
-    <col min="7425" max="7425" width="3.796875" style="74" customWidth="1"/>
-    <col min="7426" max="7426" width="5.796875" style="74" customWidth="1"/>
-    <col min="7427" max="7427" width="8.796875" style="74" customWidth="1"/>
+    <col min="7181" max="7181" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="7182" max="7424" width="11.1640625" style="74"/>
+    <col min="7425" max="7425" width="3.83203125" style="74" customWidth="1"/>
+    <col min="7426" max="7426" width="5.83203125" style="74" customWidth="1"/>
+    <col min="7427" max="7427" width="8.83203125" style="74" customWidth="1"/>
     <col min="7428" max="7428" width="26" style="74" customWidth="1"/>
     <col min="7429" max="7429" width="12.5" style="74" customWidth="1"/>
-    <col min="7430" max="7430" width="7.296875" style="74" customWidth="1"/>
-    <col min="7431" max="7431" width="13.296875" style="74" customWidth="1"/>
-    <col min="7432" max="7432" width="12.296875" style="74" customWidth="1"/>
+    <col min="7430" max="7430" width="7.33203125" style="74" customWidth="1"/>
+    <col min="7431" max="7431" width="13.33203125" style="74" customWidth="1"/>
+    <col min="7432" max="7432" width="12.33203125" style="74" customWidth="1"/>
     <col min="7433" max="7433" width="15.5" style="74" customWidth="1"/>
-    <col min="7434" max="7434" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="7435" max="7435" width="11.19921875" style="74"/>
+    <col min="7434" max="7434" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="7435" max="7435" width="11.1640625" style="74"/>
     <col min="7436" max="7436" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="7437" max="7437" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="7438" max="7680" width="11.19921875" style="74"/>
-    <col min="7681" max="7681" width="3.796875" style="74" customWidth="1"/>
-    <col min="7682" max="7682" width="5.796875" style="74" customWidth="1"/>
-    <col min="7683" max="7683" width="8.796875" style="74" customWidth="1"/>
+    <col min="7437" max="7437" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="7438" max="7680" width="11.1640625" style="74"/>
+    <col min="7681" max="7681" width="3.83203125" style="74" customWidth="1"/>
+    <col min="7682" max="7682" width="5.83203125" style="74" customWidth="1"/>
+    <col min="7683" max="7683" width="8.83203125" style="74" customWidth="1"/>
     <col min="7684" max="7684" width="26" style="74" customWidth="1"/>
     <col min="7685" max="7685" width="12.5" style="74" customWidth="1"/>
-    <col min="7686" max="7686" width="7.296875" style="74" customWidth="1"/>
-    <col min="7687" max="7687" width="13.296875" style="74" customWidth="1"/>
-    <col min="7688" max="7688" width="12.296875" style="74" customWidth="1"/>
+    <col min="7686" max="7686" width="7.33203125" style="74" customWidth="1"/>
+    <col min="7687" max="7687" width="13.33203125" style="74" customWidth="1"/>
+    <col min="7688" max="7688" width="12.33203125" style="74" customWidth="1"/>
     <col min="7689" max="7689" width="15.5" style="74" customWidth="1"/>
-    <col min="7690" max="7690" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="7691" max="7691" width="11.19921875" style="74"/>
+    <col min="7690" max="7690" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="7691" max="7691" width="11.1640625" style="74"/>
     <col min="7692" max="7692" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="7693" max="7693" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="7694" max="7936" width="11.19921875" style="74"/>
-    <col min="7937" max="7937" width="3.796875" style="74" customWidth="1"/>
-    <col min="7938" max="7938" width="5.796875" style="74" customWidth="1"/>
-    <col min="7939" max="7939" width="8.796875" style="74" customWidth="1"/>
+    <col min="7693" max="7693" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="7694" max="7936" width="11.1640625" style="74"/>
+    <col min="7937" max="7937" width="3.83203125" style="74" customWidth="1"/>
+    <col min="7938" max="7938" width="5.83203125" style="74" customWidth="1"/>
+    <col min="7939" max="7939" width="8.83203125" style="74" customWidth="1"/>
     <col min="7940" max="7940" width="26" style="74" customWidth="1"/>
     <col min="7941" max="7941" width="12.5" style="74" customWidth="1"/>
-    <col min="7942" max="7942" width="7.296875" style="74" customWidth="1"/>
-    <col min="7943" max="7943" width="13.296875" style="74" customWidth="1"/>
-    <col min="7944" max="7944" width="12.296875" style="74" customWidth="1"/>
+    <col min="7942" max="7942" width="7.33203125" style="74" customWidth="1"/>
+    <col min="7943" max="7943" width="13.33203125" style="74" customWidth="1"/>
+    <col min="7944" max="7944" width="12.33203125" style="74" customWidth="1"/>
     <col min="7945" max="7945" width="15.5" style="74" customWidth="1"/>
-    <col min="7946" max="7946" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="7947" max="7947" width="11.19921875" style="74"/>
+    <col min="7946" max="7946" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="7947" max="7947" width="11.1640625" style="74"/>
     <col min="7948" max="7948" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="7949" max="7949" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="7950" max="8192" width="11.19921875" style="74"/>
-    <col min="8193" max="8193" width="3.796875" style="74" customWidth="1"/>
-    <col min="8194" max="8194" width="5.796875" style="74" customWidth="1"/>
-    <col min="8195" max="8195" width="8.796875" style="74" customWidth="1"/>
+    <col min="7949" max="7949" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="7950" max="8192" width="11.1640625" style="74"/>
+    <col min="8193" max="8193" width="3.83203125" style="74" customWidth="1"/>
+    <col min="8194" max="8194" width="5.83203125" style="74" customWidth="1"/>
+    <col min="8195" max="8195" width="8.83203125" style="74" customWidth="1"/>
     <col min="8196" max="8196" width="26" style="74" customWidth="1"/>
     <col min="8197" max="8197" width="12.5" style="74" customWidth="1"/>
-    <col min="8198" max="8198" width="7.296875" style="74" customWidth="1"/>
-    <col min="8199" max="8199" width="13.296875" style="74" customWidth="1"/>
-    <col min="8200" max="8200" width="12.296875" style="74" customWidth="1"/>
+    <col min="8198" max="8198" width="7.33203125" style="74" customWidth="1"/>
+    <col min="8199" max="8199" width="13.33203125" style="74" customWidth="1"/>
+    <col min="8200" max="8200" width="12.33203125" style="74" customWidth="1"/>
     <col min="8201" max="8201" width="15.5" style="74" customWidth="1"/>
-    <col min="8202" max="8202" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="8203" max="8203" width="11.19921875" style="74"/>
+    <col min="8202" max="8202" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="8203" max="8203" width="11.1640625" style="74"/>
     <col min="8204" max="8204" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="8205" max="8205" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="8206" max="8448" width="11.19921875" style="74"/>
-    <col min="8449" max="8449" width="3.796875" style="74" customWidth="1"/>
-    <col min="8450" max="8450" width="5.796875" style="74" customWidth="1"/>
-    <col min="8451" max="8451" width="8.796875" style="74" customWidth="1"/>
+    <col min="8205" max="8205" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="8206" max="8448" width="11.1640625" style="74"/>
+    <col min="8449" max="8449" width="3.83203125" style="74" customWidth="1"/>
+    <col min="8450" max="8450" width="5.83203125" style="74" customWidth="1"/>
+    <col min="8451" max="8451" width="8.83203125" style="74" customWidth="1"/>
     <col min="8452" max="8452" width="26" style="74" customWidth="1"/>
     <col min="8453" max="8453" width="12.5" style="74" customWidth="1"/>
-    <col min="8454" max="8454" width="7.296875" style="74" customWidth="1"/>
-    <col min="8455" max="8455" width="13.296875" style="74" customWidth="1"/>
-    <col min="8456" max="8456" width="12.296875" style="74" customWidth="1"/>
+    <col min="8454" max="8454" width="7.33203125" style="74" customWidth="1"/>
+    <col min="8455" max="8455" width="13.33203125" style="74" customWidth="1"/>
+    <col min="8456" max="8456" width="12.33203125" style="74" customWidth="1"/>
     <col min="8457" max="8457" width="15.5" style="74" customWidth="1"/>
-    <col min="8458" max="8458" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="8459" max="8459" width="11.19921875" style="74"/>
+    <col min="8458" max="8458" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="8459" max="8459" width="11.1640625" style="74"/>
     <col min="8460" max="8460" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="8461" max="8461" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="8462" max="8704" width="11.19921875" style="74"/>
-    <col min="8705" max="8705" width="3.796875" style="74" customWidth="1"/>
-    <col min="8706" max="8706" width="5.796875" style="74" customWidth="1"/>
-    <col min="8707" max="8707" width="8.796875" style="74" customWidth="1"/>
+    <col min="8461" max="8461" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="8462" max="8704" width="11.1640625" style="74"/>
+    <col min="8705" max="8705" width="3.83203125" style="74" customWidth="1"/>
+    <col min="8706" max="8706" width="5.83203125" style="74" customWidth="1"/>
+    <col min="8707" max="8707" width="8.83203125" style="74" customWidth="1"/>
     <col min="8708" max="8708" width="26" style="74" customWidth="1"/>
     <col min="8709" max="8709" width="12.5" style="74" customWidth="1"/>
-    <col min="8710" max="8710" width="7.296875" style="74" customWidth="1"/>
-    <col min="8711" max="8711" width="13.296875" style="74" customWidth="1"/>
-    <col min="8712" max="8712" width="12.296875" style="74" customWidth="1"/>
+    <col min="8710" max="8710" width="7.33203125" style="74" customWidth="1"/>
+    <col min="8711" max="8711" width="13.33203125" style="74" customWidth="1"/>
+    <col min="8712" max="8712" width="12.33203125" style="74" customWidth="1"/>
     <col min="8713" max="8713" width="15.5" style="74" customWidth="1"/>
-    <col min="8714" max="8714" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="8715" max="8715" width="11.19921875" style="74"/>
+    <col min="8714" max="8714" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="8715" max="8715" width="11.1640625" style="74"/>
     <col min="8716" max="8716" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="8717" max="8717" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="8718" max="8960" width="11.19921875" style="74"/>
-    <col min="8961" max="8961" width="3.796875" style="74" customWidth="1"/>
-    <col min="8962" max="8962" width="5.796875" style="74" customWidth="1"/>
-    <col min="8963" max="8963" width="8.796875" style="74" customWidth="1"/>
+    <col min="8717" max="8717" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="8718" max="8960" width="11.1640625" style="74"/>
+    <col min="8961" max="8961" width="3.83203125" style="74" customWidth="1"/>
+    <col min="8962" max="8962" width="5.83203125" style="74" customWidth="1"/>
+    <col min="8963" max="8963" width="8.83203125" style="74" customWidth="1"/>
     <col min="8964" max="8964" width="26" style="74" customWidth="1"/>
     <col min="8965" max="8965" width="12.5" style="74" customWidth="1"/>
-    <col min="8966" max="8966" width="7.296875" style="74" customWidth="1"/>
-    <col min="8967" max="8967" width="13.296875" style="74" customWidth="1"/>
-    <col min="8968" max="8968" width="12.296875" style="74" customWidth="1"/>
+    <col min="8966" max="8966" width="7.33203125" style="74" customWidth="1"/>
+    <col min="8967" max="8967" width="13.33203125" style="74" customWidth="1"/>
+    <col min="8968" max="8968" width="12.33203125" style="74" customWidth="1"/>
     <col min="8969" max="8969" width="15.5" style="74" customWidth="1"/>
-    <col min="8970" max="8970" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="8971" max="8971" width="11.19921875" style="74"/>
+    <col min="8970" max="8970" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="8971" max="8971" width="11.1640625" style="74"/>
     <col min="8972" max="8972" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="8973" max="8973" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="8974" max="9216" width="11.19921875" style="74"/>
-    <col min="9217" max="9217" width="3.796875" style="74" customWidth="1"/>
-    <col min="9218" max="9218" width="5.796875" style="74" customWidth="1"/>
-    <col min="9219" max="9219" width="8.796875" style="74" customWidth="1"/>
+    <col min="8973" max="8973" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="8974" max="9216" width="11.1640625" style="74"/>
+    <col min="9217" max="9217" width="3.83203125" style="74" customWidth="1"/>
+    <col min="9218" max="9218" width="5.83203125" style="74" customWidth="1"/>
+    <col min="9219" max="9219" width="8.83203125" style="74" customWidth="1"/>
     <col min="9220" max="9220" width="26" style="74" customWidth="1"/>
     <col min="9221" max="9221" width="12.5" style="74" customWidth="1"/>
-    <col min="9222" max="9222" width="7.296875" style="74" customWidth="1"/>
-    <col min="9223" max="9223" width="13.296875" style="74" customWidth="1"/>
-    <col min="9224" max="9224" width="12.296875" style="74" customWidth="1"/>
+    <col min="9222" max="9222" width="7.33203125" style="74" customWidth="1"/>
+    <col min="9223" max="9223" width="13.33203125" style="74" customWidth="1"/>
+    <col min="9224" max="9224" width="12.33203125" style="74" customWidth="1"/>
     <col min="9225" max="9225" width="15.5" style="74" customWidth="1"/>
-    <col min="9226" max="9226" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="9227" max="9227" width="11.19921875" style="74"/>
+    <col min="9226" max="9226" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="9227" max="9227" width="11.1640625" style="74"/>
     <col min="9228" max="9228" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="9229" max="9229" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="9230" max="9472" width="11.19921875" style="74"/>
-    <col min="9473" max="9473" width="3.796875" style="74" customWidth="1"/>
-    <col min="9474" max="9474" width="5.796875" style="74" customWidth="1"/>
-    <col min="9475" max="9475" width="8.796875" style="74" customWidth="1"/>
+    <col min="9229" max="9229" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="9230" max="9472" width="11.1640625" style="74"/>
+    <col min="9473" max="9473" width="3.83203125" style="74" customWidth="1"/>
+    <col min="9474" max="9474" width="5.83203125" style="74" customWidth="1"/>
+    <col min="9475" max="9475" width="8.83203125" style="74" customWidth="1"/>
     <col min="9476" max="9476" width="26" style="74" customWidth="1"/>
     <col min="9477" max="9477" width="12.5" style="74" customWidth="1"/>
-    <col min="9478" max="9478" width="7.296875" style="74" customWidth="1"/>
-    <col min="9479" max="9479" width="13.296875" style="74" customWidth="1"/>
-    <col min="9480" max="9480" width="12.296875" style="74" customWidth="1"/>
+    <col min="9478" max="9478" width="7.33203125" style="74" customWidth="1"/>
+    <col min="9479" max="9479" width="13.33203125" style="74" customWidth="1"/>
+    <col min="9480" max="9480" width="12.33203125" style="74" customWidth="1"/>
     <col min="9481" max="9481" width="15.5" style="74" customWidth="1"/>
-    <col min="9482" max="9482" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="9483" max="9483" width="11.19921875" style="74"/>
+    <col min="9482" max="9482" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="9483" max="9483" width="11.1640625" style="74"/>
     <col min="9484" max="9484" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="9485" max="9485" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="9486" max="9728" width="11.19921875" style="74"/>
-    <col min="9729" max="9729" width="3.796875" style="74" customWidth="1"/>
-    <col min="9730" max="9730" width="5.796875" style="74" customWidth="1"/>
-    <col min="9731" max="9731" width="8.796875" style="74" customWidth="1"/>
+    <col min="9485" max="9485" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="9486" max="9728" width="11.1640625" style="74"/>
+    <col min="9729" max="9729" width="3.83203125" style="74" customWidth="1"/>
+    <col min="9730" max="9730" width="5.83203125" style="74" customWidth="1"/>
+    <col min="9731" max="9731" width="8.83203125" style="74" customWidth="1"/>
     <col min="9732" max="9732" width="26" style="74" customWidth="1"/>
     <col min="9733" max="9733" width="12.5" style="74" customWidth="1"/>
-    <col min="9734" max="9734" width="7.296875" style="74" customWidth="1"/>
-    <col min="9735" max="9735" width="13.296875" style="74" customWidth="1"/>
-    <col min="9736" max="9736" width="12.296875" style="74" customWidth="1"/>
+    <col min="9734" max="9734" width="7.33203125" style="74" customWidth="1"/>
+    <col min="9735" max="9735" width="13.33203125" style="74" customWidth="1"/>
+    <col min="9736" max="9736" width="12.33203125" style="74" customWidth="1"/>
     <col min="9737" max="9737" width="15.5" style="74" customWidth="1"/>
-    <col min="9738" max="9738" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="9739" max="9739" width="11.19921875" style="74"/>
+    <col min="9738" max="9738" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="9739" max="9739" width="11.1640625" style="74"/>
     <col min="9740" max="9740" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="9741" max="9741" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="9742" max="9984" width="11.19921875" style="74"/>
-    <col min="9985" max="9985" width="3.796875" style="74" customWidth="1"/>
-    <col min="9986" max="9986" width="5.796875" style="74" customWidth="1"/>
-    <col min="9987" max="9987" width="8.796875" style="74" customWidth="1"/>
+    <col min="9741" max="9741" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="9742" max="9984" width="11.1640625" style="74"/>
+    <col min="9985" max="9985" width="3.83203125" style="74" customWidth="1"/>
+    <col min="9986" max="9986" width="5.83203125" style="74" customWidth="1"/>
+    <col min="9987" max="9987" width="8.83203125" style="74" customWidth="1"/>
     <col min="9988" max="9988" width="26" style="74" customWidth="1"/>
     <col min="9989" max="9989" width="12.5" style="74" customWidth="1"/>
-    <col min="9990" max="9990" width="7.296875" style="74" customWidth="1"/>
-    <col min="9991" max="9991" width="13.296875" style="74" customWidth="1"/>
-    <col min="9992" max="9992" width="12.296875" style="74" customWidth="1"/>
+    <col min="9990" max="9990" width="7.33203125" style="74" customWidth="1"/>
+    <col min="9991" max="9991" width="13.33203125" style="74" customWidth="1"/>
+    <col min="9992" max="9992" width="12.33203125" style="74" customWidth="1"/>
     <col min="9993" max="9993" width="15.5" style="74" customWidth="1"/>
-    <col min="9994" max="9994" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="9995" max="9995" width="11.19921875" style="74"/>
+    <col min="9994" max="9994" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="9995" max="9995" width="11.1640625" style="74"/>
     <col min="9996" max="9996" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="9997" max="9997" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="9998" max="10240" width="11.19921875" style="74"/>
-    <col min="10241" max="10241" width="3.796875" style="74" customWidth="1"/>
-    <col min="10242" max="10242" width="5.796875" style="74" customWidth="1"/>
-    <col min="10243" max="10243" width="8.796875" style="74" customWidth="1"/>
+    <col min="9997" max="9997" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="9998" max="10240" width="11.1640625" style="74"/>
+    <col min="10241" max="10241" width="3.83203125" style="74" customWidth="1"/>
+    <col min="10242" max="10242" width="5.83203125" style="74" customWidth="1"/>
+    <col min="10243" max="10243" width="8.83203125" style="74" customWidth="1"/>
     <col min="10244" max="10244" width="26" style="74" customWidth="1"/>
     <col min="10245" max="10245" width="12.5" style="74" customWidth="1"/>
-    <col min="10246" max="10246" width="7.296875" style="74" customWidth="1"/>
-    <col min="10247" max="10247" width="13.296875" style="74" customWidth="1"/>
-    <col min="10248" max="10248" width="12.296875" style="74" customWidth="1"/>
+    <col min="10246" max="10246" width="7.33203125" style="74" customWidth="1"/>
+    <col min="10247" max="10247" width="13.33203125" style="74" customWidth="1"/>
+    <col min="10248" max="10248" width="12.33203125" style="74" customWidth="1"/>
     <col min="10249" max="10249" width="15.5" style="74" customWidth="1"/>
-    <col min="10250" max="10250" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="10251" max="10251" width="11.19921875" style="74"/>
+    <col min="10250" max="10250" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="10251" max="10251" width="11.1640625" style="74"/>
     <col min="10252" max="10252" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="10253" max="10253" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="10254" max="10496" width="11.19921875" style="74"/>
-    <col min="10497" max="10497" width="3.796875" style="74" customWidth="1"/>
-    <col min="10498" max="10498" width="5.796875" style="74" customWidth="1"/>
-    <col min="10499" max="10499" width="8.796875" style="74" customWidth="1"/>
+    <col min="10253" max="10253" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="10254" max="10496" width="11.1640625" style="74"/>
+    <col min="10497" max="10497" width="3.83203125" style="74" customWidth="1"/>
+    <col min="10498" max="10498" width="5.83203125" style="74" customWidth="1"/>
+    <col min="10499" max="10499" width="8.83203125" style="74" customWidth="1"/>
     <col min="10500" max="10500" width="26" style="74" customWidth="1"/>
     <col min="10501" max="10501" width="12.5" style="74" customWidth="1"/>
-    <col min="10502" max="10502" width="7.296875" style="74" customWidth="1"/>
-    <col min="10503" max="10503" width="13.296875" style="74" customWidth="1"/>
-    <col min="10504" max="10504" width="12.296875" style="74" customWidth="1"/>
+    <col min="10502" max="10502" width="7.33203125" style="74" customWidth="1"/>
+    <col min="10503" max="10503" width="13.33203125" style="74" customWidth="1"/>
+    <col min="10504" max="10504" width="12.33203125" style="74" customWidth="1"/>
     <col min="10505" max="10505" width="15.5" style="74" customWidth="1"/>
-    <col min="10506" max="10506" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="10507" max="10507" width="11.19921875" style="74"/>
+    <col min="10506" max="10506" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="10507" max="10507" width="11.1640625" style="74"/>
     <col min="10508" max="10508" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="10509" max="10509" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="10510" max="10752" width="11.19921875" style="74"/>
-    <col min="10753" max="10753" width="3.796875" style="74" customWidth="1"/>
-    <col min="10754" max="10754" width="5.796875" style="74" customWidth="1"/>
-    <col min="10755" max="10755" width="8.796875" style="74" customWidth="1"/>
+    <col min="10509" max="10509" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="10510" max="10752" width="11.1640625" style="74"/>
+    <col min="10753" max="10753" width="3.83203125" style="74" customWidth="1"/>
+    <col min="10754" max="10754" width="5.83203125" style="74" customWidth="1"/>
+    <col min="10755" max="10755" width="8.83203125" style="74" customWidth="1"/>
     <col min="10756" max="10756" width="26" style="74" customWidth="1"/>
     <col min="10757" max="10757" width="12.5" style="74" customWidth="1"/>
-    <col min="10758" max="10758" width="7.296875" style="74" customWidth="1"/>
-    <col min="10759" max="10759" width="13.296875" style="74" customWidth="1"/>
-    <col min="10760" max="10760" width="12.296875" style="74" customWidth="1"/>
+    <col min="10758" max="10758" width="7.33203125" style="74" customWidth="1"/>
+    <col min="10759" max="10759" width="13.33203125" style="74" customWidth="1"/>
+    <col min="10760" max="10760" width="12.33203125" style="74" customWidth="1"/>
     <col min="10761" max="10761" width="15.5" style="74" customWidth="1"/>
-    <col min="10762" max="10762" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="10763" max="10763" width="11.19921875" style="74"/>
+    <col min="10762" max="10762" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="10763" max="10763" width="11.1640625" style="74"/>
     <col min="10764" max="10764" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="10765" max="10765" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="10766" max="11008" width="11.19921875" style="74"/>
-    <col min="11009" max="11009" width="3.796875" style="74" customWidth="1"/>
-    <col min="11010" max="11010" width="5.796875" style="74" customWidth="1"/>
-    <col min="11011" max="11011" width="8.796875" style="74" customWidth="1"/>
+    <col min="10765" max="10765" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="10766" max="11008" width="11.1640625" style="74"/>
+    <col min="11009" max="11009" width="3.83203125" style="74" customWidth="1"/>
+    <col min="11010" max="11010" width="5.83203125" style="74" customWidth="1"/>
+    <col min="11011" max="11011" width="8.83203125" style="74" customWidth="1"/>
     <col min="11012" max="11012" width="26" style="74" customWidth="1"/>
     <col min="11013" max="11013" width="12.5" style="74" customWidth="1"/>
-    <col min="11014" max="11014" width="7.296875" style="74" customWidth="1"/>
-    <col min="11015" max="11015" width="13.296875" style="74" customWidth="1"/>
-    <col min="11016" max="11016" width="12.296875" style="74" customWidth="1"/>
+    <col min="11014" max="11014" width="7.33203125" style="74" customWidth="1"/>
+    <col min="11015" max="11015" width="13.33203125" style="74" customWidth="1"/>
+    <col min="11016" max="11016" width="12.33203125" style="74" customWidth="1"/>
     <col min="11017" max="11017" width="15.5" style="74" customWidth="1"/>
-    <col min="11018" max="11018" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11019" max="11019" width="11.19921875" style="74"/>
+    <col min="11018" max="11018" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11019" max="11019" width="11.1640625" style="74"/>
     <col min="11020" max="11020" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="11021" max="11021" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11022" max="11264" width="11.19921875" style="74"/>
-    <col min="11265" max="11265" width="3.796875" style="74" customWidth="1"/>
-    <col min="11266" max="11266" width="5.796875" style="74" customWidth="1"/>
-    <col min="11267" max="11267" width="8.796875" style="74" customWidth="1"/>
+    <col min="11021" max="11021" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11022" max="11264" width="11.1640625" style="74"/>
+    <col min="11265" max="11265" width="3.83203125" style="74" customWidth="1"/>
+    <col min="11266" max="11266" width="5.83203125" style="74" customWidth="1"/>
+    <col min="11267" max="11267" width="8.83203125" style="74" customWidth="1"/>
     <col min="11268" max="11268" width="26" style="74" customWidth="1"/>
     <col min="11269" max="11269" width="12.5" style="74" customWidth="1"/>
-    <col min="11270" max="11270" width="7.296875" style="74" customWidth="1"/>
-    <col min="11271" max="11271" width="13.296875" style="74" customWidth="1"/>
-    <col min="11272" max="11272" width="12.296875" style="74" customWidth="1"/>
+    <col min="11270" max="11270" width="7.33203125" style="74" customWidth="1"/>
+    <col min="11271" max="11271" width="13.33203125" style="74" customWidth="1"/>
+    <col min="11272" max="11272" width="12.33203125" style="74" customWidth="1"/>
     <col min="11273" max="11273" width="15.5" style="74" customWidth="1"/>
-    <col min="11274" max="11274" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11275" max="11275" width="11.19921875" style="74"/>
+    <col min="11274" max="11274" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11275" max="11275" width="11.1640625" style="74"/>
     <col min="11276" max="11276" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="11277" max="11277" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11278" max="11520" width="11.19921875" style="74"/>
-    <col min="11521" max="11521" width="3.796875" style="74" customWidth="1"/>
-    <col min="11522" max="11522" width="5.796875" style="74" customWidth="1"/>
-    <col min="11523" max="11523" width="8.796875" style="74" customWidth="1"/>
+    <col min="11277" max="11277" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11278" max="11520" width="11.1640625" style="74"/>
+    <col min="11521" max="11521" width="3.83203125" style="74" customWidth="1"/>
+    <col min="11522" max="11522" width="5.83203125" style="74" customWidth="1"/>
+    <col min="11523" max="11523" width="8.83203125" style="74" customWidth="1"/>
     <col min="11524" max="11524" width="26" style="74" customWidth="1"/>
     <col min="11525" max="11525" width="12.5" style="74" customWidth="1"/>
-    <col min="11526" max="11526" width="7.296875" style="74" customWidth="1"/>
-    <col min="11527" max="11527" width="13.296875" style="74" customWidth="1"/>
-    <col min="11528" max="11528" width="12.296875" style="74" customWidth="1"/>
+    <col min="11526" max="11526" width="7.33203125" style="74" customWidth="1"/>
+    <col min="11527" max="11527" width="13.33203125" style="74" customWidth="1"/>
+    <col min="11528" max="11528" width="12.33203125" style="74" customWidth="1"/>
     <col min="11529" max="11529" width="15.5" style="74" customWidth="1"/>
-    <col min="11530" max="11530" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11531" max="11531" width="11.19921875" style="74"/>
+    <col min="11530" max="11530" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11531" max="11531" width="11.1640625" style="74"/>
     <col min="11532" max="11532" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="11533" max="11533" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11534" max="11776" width="11.19921875" style="74"/>
-    <col min="11777" max="11777" width="3.796875" style="74" customWidth="1"/>
-    <col min="11778" max="11778" width="5.796875" style="74" customWidth="1"/>
-    <col min="11779" max="11779" width="8.796875" style="74" customWidth="1"/>
+    <col min="11533" max="11533" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11534" max="11776" width="11.1640625" style="74"/>
+    <col min="11777" max="11777" width="3.83203125" style="74" customWidth="1"/>
+    <col min="11778" max="11778" width="5.83203125" style="74" customWidth="1"/>
+    <col min="11779" max="11779" width="8.83203125" style="74" customWidth="1"/>
     <col min="11780" max="11780" width="26" style="74" customWidth="1"/>
     <col min="11781" max="11781" width="12.5" style="74" customWidth="1"/>
-    <col min="11782" max="11782" width="7.296875" style="74" customWidth="1"/>
-    <col min="11783" max="11783" width="13.296875" style="74" customWidth="1"/>
-    <col min="11784" max="11784" width="12.296875" style="74" customWidth="1"/>
+    <col min="11782" max="11782" width="7.33203125" style="74" customWidth="1"/>
+    <col min="11783" max="11783" width="13.33203125" style="74" customWidth="1"/>
+    <col min="11784" max="11784" width="12.33203125" style="74" customWidth="1"/>
     <col min="11785" max="11785" width="15.5" style="74" customWidth="1"/>
-    <col min="11786" max="11786" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11787" max="11787" width="11.19921875" style="74"/>
+    <col min="11786" max="11786" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11787" max="11787" width="11.1640625" style="74"/>
     <col min="11788" max="11788" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="11789" max="11789" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="11790" max="12032" width="11.19921875" style="74"/>
-    <col min="12033" max="12033" width="3.796875" style="74" customWidth="1"/>
-    <col min="12034" max="12034" width="5.796875" style="74" customWidth="1"/>
-    <col min="12035" max="12035" width="8.796875" style="74" customWidth="1"/>
+    <col min="11789" max="11789" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="11790" max="12032" width="11.1640625" style="74"/>
+    <col min="12033" max="12033" width="3.83203125" style="74" customWidth="1"/>
+    <col min="12034" max="12034" width="5.83203125" style="74" customWidth="1"/>
+    <col min="12035" max="12035" width="8.83203125" style="74" customWidth="1"/>
     <col min="12036" max="12036" width="26" style="74" customWidth="1"/>
     <col min="12037" max="12037" width="12.5" style="74" customWidth="1"/>
-    <col min="12038" max="12038" width="7.296875" style="74" customWidth="1"/>
-    <col min="12039" max="12039" width="13.296875" style="74" customWidth="1"/>
-    <col min="12040" max="12040" width="12.296875" style="74" customWidth="1"/>
+    <col min="12038" max="12038" width="7.33203125" style="74" customWidth="1"/>
+    <col min="12039" max="12039" width="13.33203125" style="74" customWidth="1"/>
+    <col min="12040" max="12040" width="12.33203125" style="74" customWidth="1"/>
     <col min="12041" max="12041" width="15.5" style="74" customWidth="1"/>
-    <col min="12042" max="12042" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="12043" max="12043" width="11.19921875" style="74"/>
+    <col min="12042" max="12042" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="12043" max="12043" width="11.1640625" style="74"/>
     <col min="12044" max="12044" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="12045" max="12045" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="12046" max="12288" width="11.19921875" style="74"/>
-    <col min="12289" max="12289" width="3.796875" style="74" customWidth="1"/>
-    <col min="12290" max="12290" width="5.796875" style="74" customWidth="1"/>
-    <col min="12291" max="12291" width="8.796875" style="74" customWidth="1"/>
+    <col min="12045" max="12045" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="12046" max="12288" width="11.1640625" style="74"/>
+    <col min="12289" max="12289" width="3.83203125" style="74" customWidth="1"/>
+    <col min="12290" max="12290" width="5.83203125" style="74" customWidth="1"/>
+    <col min="12291" max="12291" width="8.83203125" style="74" customWidth="1"/>
     <col min="12292" max="12292" width="26" style="74" customWidth="1"/>
     <col min="12293" max="12293" width="12.5" style="74" customWidth="1"/>
-    <col min="12294" max="12294" width="7.296875" style="74" customWidth="1"/>
-    <col min="12295" max="12295" width="13.296875" style="74" customWidth="1"/>
-    <col min="12296" max="12296" width="12.296875" style="74" customWidth="1"/>
+    <col min="12294" max="12294" width="7.33203125" style="74" customWidth="1"/>
+    <col min="12295" max="12295" width="13.33203125" style="74" customWidth="1"/>
+    <col min="12296" max="12296" width="12.33203125" style="74" customWidth="1"/>
     <col min="12297" max="12297" width="15.5" style="74" customWidth="1"/>
-    <col min="12298" max="12298" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="12299" max="12299" width="11.19921875" style="74"/>
+    <col min="12298" max="12298" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="12299" max="12299" width="11.1640625" style="74"/>
     <col min="12300" max="12300" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="12301" max="12301" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="12302" max="12544" width="11.19921875" style="74"/>
-    <col min="12545" max="12545" width="3.796875" style="74" customWidth="1"/>
-    <col min="12546" max="12546" width="5.796875" style="74" customWidth="1"/>
-    <col min="12547" max="12547" width="8.796875" style="74" customWidth="1"/>
+    <col min="12301" max="12301" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="12302" max="12544" width="11.1640625" style="74"/>
+    <col min="12545" max="12545" width="3.83203125" style="74" customWidth="1"/>
+    <col min="12546" max="12546" width="5.83203125" style="74" customWidth="1"/>
+    <col min="12547" max="12547" width="8.83203125" style="74" customWidth="1"/>
     <col min="12548" max="12548" width="26" style="74" customWidth="1"/>
     <col min="12549" max="12549" width="12.5" style="74" customWidth="1"/>
-    <col min="12550" max="12550" width="7.296875" style="74" customWidth="1"/>
-    <col min="12551" max="12551" width="13.296875" style="74" customWidth="1"/>
-    <col min="12552" max="12552" width="12.296875" style="74" customWidth="1"/>
+    <col min="12550" max="12550" width="7.33203125" style="74" customWidth="1"/>
+    <col min="12551" max="12551" width="13.33203125" style="74" customWidth="1"/>
+    <col min="12552" max="12552" width="12.33203125" style="74" customWidth="1"/>
     <col min="12553" max="12553" width="15.5" style="74" customWidth="1"/>
-    <col min="12554" max="12554" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="12555" max="12555" width="11.19921875" style="74"/>
+    <col min="12554" max="12554" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="12555" max="12555" width="11.1640625" style="74"/>
     <col min="12556" max="12556" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="12557" max="12557" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="12558" max="12800" width="11.19921875" style="74"/>
-    <col min="12801" max="12801" width="3.796875" style="74" customWidth="1"/>
-    <col min="12802" max="12802" width="5.796875" style="74" customWidth="1"/>
-    <col min="12803" max="12803" width="8.796875" style="74" customWidth="1"/>
+    <col min="12557" max="12557" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="12558" max="12800" width="11.1640625" style="74"/>
+    <col min="12801" max="12801" width="3.83203125" style="74" customWidth="1"/>
+    <col min="12802" max="12802" width="5.83203125" style="74" customWidth="1"/>
+    <col min="12803" max="12803" width="8.83203125" style="74" customWidth="1"/>
     <col min="12804" max="12804" width="26" style="74" customWidth="1"/>
     <col min="12805" max="12805" width="12.5" style="74" customWidth="1"/>
-    <col min="12806" max="12806" width="7.296875" style="74" customWidth="1"/>
-    <col min="12807" max="12807" width="13.296875" style="74" customWidth="1"/>
-    <col min="12808" max="12808" width="12.296875" style="74" customWidth="1"/>
+    <col min="12806" max="12806" width="7.33203125" style="74" customWidth="1"/>
+    <col min="12807" max="12807" width="13.33203125" style="74" customWidth="1"/>
+    <col min="12808" max="12808" width="12.33203125" style="74" customWidth="1"/>
     <col min="12809" max="12809" width="15.5" style="74" customWidth="1"/>
-    <col min="12810" max="12810" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="12811" max="12811" width="11.19921875" style="74"/>
+    <col min="12810" max="12810" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="12811" max="12811" width="11.1640625" style="74"/>
     <col min="12812" max="12812" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="12813" max="12813" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="12814" max="13056" width="11.19921875" style="74"/>
-    <col min="13057" max="13057" width="3.796875" style="74" customWidth="1"/>
-    <col min="13058" max="13058" width="5.796875" style="74" customWidth="1"/>
-    <col min="13059" max="13059" width="8.796875" style="74" customWidth="1"/>
+    <col min="12813" max="12813" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="12814" max="13056" width="11.1640625" style="74"/>
+    <col min="13057" max="13057" width="3.83203125" style="74" customWidth="1"/>
+    <col min="13058" max="13058" width="5.83203125" style="74" customWidth="1"/>
+    <col min="13059" max="13059" width="8.83203125" style="74" customWidth="1"/>
     <col min="13060" max="13060" width="26" style="74" customWidth="1"/>
     <col min="13061" max="13061" width="12.5" style="74" customWidth="1"/>
-    <col min="13062" max="13062" width="7.296875" style="74" customWidth="1"/>
-    <col min="13063" max="13063" width="13.296875" style="74" customWidth="1"/>
-    <col min="13064" max="13064" width="12.296875" style="74" customWidth="1"/>
+    <col min="13062" max="13062" width="7.33203125" style="74" customWidth="1"/>
+    <col min="13063" max="13063" width="13.33203125" style="74" customWidth="1"/>
+    <col min="13064" max="13064" width="12.33203125" style="74" customWidth="1"/>
     <col min="13065" max="13065" width="15.5" style="74" customWidth="1"/>
-    <col min="13066" max="13066" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="13067" max="13067" width="11.19921875" style="74"/>
+    <col min="13066" max="13066" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="13067" max="13067" width="11.1640625" style="74"/>
     <col min="13068" max="13068" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="13069" max="13069" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="13070" max="13312" width="11.19921875" style="74"/>
-    <col min="13313" max="13313" width="3.796875" style="74" customWidth="1"/>
-    <col min="13314" max="13314" width="5.796875" style="74" customWidth="1"/>
-    <col min="13315" max="13315" width="8.796875" style="74" customWidth="1"/>
+    <col min="13069" max="13069" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="13070" max="13312" width="11.1640625" style="74"/>
+    <col min="13313" max="13313" width="3.83203125" style="74" customWidth="1"/>
+    <col min="13314" max="13314" width="5.83203125" style="74" customWidth="1"/>
+    <col min="13315" max="13315" width="8.83203125" style="74" customWidth="1"/>
     <col min="13316" max="13316" width="26" style="74" customWidth="1"/>
     <col min="13317" max="13317" width="12.5" style="74" customWidth="1"/>
-    <col min="13318" max="13318" width="7.296875" style="74" customWidth="1"/>
-    <col min="13319" max="13319" width="13.296875" style="74" customWidth="1"/>
-    <col min="13320" max="13320" width="12.296875" style="74" customWidth="1"/>
+    <col min="13318" max="13318" width="7.33203125" style="74" customWidth="1"/>
+    <col min="13319" max="13319" width="13.33203125" style="74" customWidth="1"/>
+    <col min="13320" max="13320" width="12.33203125" style="74" customWidth="1"/>
     <col min="13321" max="13321" width="15.5" style="74" customWidth="1"/>
-    <col min="13322" max="13322" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="13323" max="13323" width="11.19921875" style="74"/>
+    <col min="13322" max="13322" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="13323" max="13323" width="11.1640625" style="74"/>
     <col min="13324" max="13324" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="13325" max="13325" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="13326" max="13568" width="11.19921875" style="74"/>
-    <col min="13569" max="13569" width="3.796875" style="74" customWidth="1"/>
-    <col min="13570" max="13570" width="5.796875" style="74" customWidth="1"/>
-    <col min="13571" max="13571" width="8.796875" style="74" customWidth="1"/>
+    <col min="13325" max="13325" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="13326" max="13568" width="11.1640625" style="74"/>
+    <col min="13569" max="13569" width="3.83203125" style="74" customWidth="1"/>
+    <col min="13570" max="13570" width="5.83203125" style="74" customWidth="1"/>
+    <col min="13571" max="13571" width="8.83203125" style="74" customWidth="1"/>
     <col min="13572" max="13572" width="26" style="74" customWidth="1"/>
     <col min="13573" max="13573" width="12.5" style="74" customWidth="1"/>
-    <col min="13574" max="13574" width="7.296875" style="74" customWidth="1"/>
-    <col min="13575" max="13575" width="13.296875" style="74" customWidth="1"/>
-    <col min="13576" max="13576" width="12.296875" style="74" customWidth="1"/>
+    <col min="13574" max="13574" width="7.33203125" style="74" customWidth="1"/>
+    <col min="13575" max="13575" width="13.33203125" style="74" customWidth="1"/>
+    <col min="13576" max="13576" width="12.33203125" style="74" customWidth="1"/>
     <col min="13577" max="13577" width="15.5" style="74" customWidth="1"/>
-    <col min="13578" max="13578" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="13579" max="13579" width="11.19921875" style="74"/>
+    <col min="13578" max="13578" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="13579" max="13579" width="11.1640625" style="74"/>
     <col min="13580" max="13580" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="13581" max="13581" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="13582" max="13824" width="11.19921875" style="74"/>
-    <col min="13825" max="13825" width="3.796875" style="74" customWidth="1"/>
-    <col min="13826" max="13826" width="5.796875" style="74" customWidth="1"/>
-    <col min="13827" max="13827" width="8.796875" style="74" customWidth="1"/>
+    <col min="13581" max="13581" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="13582" max="13824" width="11.1640625" style="74"/>
+    <col min="13825" max="13825" width="3.83203125" style="74" customWidth="1"/>
+    <col min="13826" max="13826" width="5.83203125" style="74" customWidth="1"/>
+    <col min="13827" max="13827" width="8.83203125" style="74" customWidth="1"/>
     <col min="13828" max="13828" width="26" style="74" customWidth="1"/>
     <col min="13829" max="13829" width="12.5" style="74" customWidth="1"/>
-    <col min="13830" max="13830" width="7.296875" style="74" customWidth="1"/>
-    <col min="13831" max="13831" width="13.296875" style="74" customWidth="1"/>
-    <col min="13832" max="13832" width="12.296875" style="74" customWidth="1"/>
+    <col min="13830" max="13830" width="7.33203125" style="74" customWidth="1"/>
+    <col min="13831" max="13831" width="13.33203125" style="74" customWidth="1"/>
+    <col min="13832" max="13832" width="12.33203125" style="74" customWidth="1"/>
     <col min="13833" max="13833" width="15.5" style="74" customWidth="1"/>
-    <col min="13834" max="13834" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="13835" max="13835" width="11.19921875" style="74"/>
+    <col min="13834" max="13834" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="13835" max="13835" width="11.1640625" style="74"/>
     <col min="13836" max="13836" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="13837" max="13837" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="13838" max="14080" width="11.19921875" style="74"/>
-    <col min="14081" max="14081" width="3.796875" style="74" customWidth="1"/>
-    <col min="14082" max="14082" width="5.796875" style="74" customWidth="1"/>
-    <col min="14083" max="14083" width="8.796875" style="74" customWidth="1"/>
+    <col min="13837" max="13837" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="13838" max="14080" width="11.1640625" style="74"/>
+    <col min="14081" max="14081" width="3.83203125" style="74" customWidth="1"/>
+    <col min="14082" max="14082" width="5.83203125" style="74" customWidth="1"/>
+    <col min="14083" max="14083" width="8.83203125" style="74" customWidth="1"/>
     <col min="14084" max="14084" width="26" style="74" customWidth="1"/>
     <col min="14085" max="14085" width="12.5" style="74" customWidth="1"/>
-    <col min="14086" max="14086" width="7.296875" style="74" customWidth="1"/>
-    <col min="14087" max="14087" width="13.296875" style="74" customWidth="1"/>
-    <col min="14088" max="14088" width="12.296875" style="74" customWidth="1"/>
+    <col min="14086" max="14086" width="7.33203125" style="74" customWidth="1"/>
+    <col min="14087" max="14087" width="13.33203125" style="74" customWidth="1"/>
+    <col min="14088" max="14088" width="12.33203125" style="74" customWidth="1"/>
     <col min="14089" max="14089" width="15.5" style="74" customWidth="1"/>
-    <col min="14090" max="14090" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="14091" max="14091" width="11.19921875" style="74"/>
+    <col min="14090" max="14090" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="14091" max="14091" width="11.1640625" style="74"/>
     <col min="14092" max="14092" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="14093" max="14093" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="14094" max="14336" width="11.19921875" style="74"/>
-    <col min="14337" max="14337" width="3.796875" style="74" customWidth="1"/>
-    <col min="14338" max="14338" width="5.796875" style="74" customWidth="1"/>
-    <col min="14339" max="14339" width="8.796875" style="74" customWidth="1"/>
+    <col min="14093" max="14093" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="14094" max="14336" width="11.1640625" style="74"/>
+    <col min="14337" max="14337" width="3.83203125" style="74" customWidth="1"/>
+    <col min="14338" max="14338" width="5.83203125" style="74" customWidth="1"/>
+    <col min="14339" max="14339" width="8.83203125" style="74" customWidth="1"/>
     <col min="14340" max="14340" width="26" style="74" customWidth="1"/>
     <col min="14341" max="14341" width="12.5" style="74" customWidth="1"/>
-    <col min="14342" max="14342" width="7.296875" style="74" customWidth="1"/>
-    <col min="14343" max="14343" width="13.296875" style="74" customWidth="1"/>
-    <col min="14344" max="14344" width="12.296875" style="74" customWidth="1"/>
+    <col min="14342" max="14342" width="7.33203125" style="74" customWidth="1"/>
+    <col min="14343" max="14343" width="13.33203125" style="74" customWidth="1"/>
+    <col min="14344" max="14344" width="12.33203125" style="74" customWidth="1"/>
     <col min="14345" max="14345" width="15.5" style="74" customWidth="1"/>
-    <col min="14346" max="14346" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="14347" max="14347" width="11.19921875" style="74"/>
+    <col min="14346" max="14346" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="14347" max="14347" width="11.1640625" style="74"/>
     <col min="14348" max="14348" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="14349" max="14349" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="14350" max="14592" width="11.19921875" style="74"/>
-    <col min="14593" max="14593" width="3.796875" style="74" customWidth="1"/>
-    <col min="14594" max="14594" width="5.796875" style="74" customWidth="1"/>
-    <col min="14595" max="14595" width="8.796875" style="74" customWidth="1"/>
+    <col min="14349" max="14349" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="14350" max="14592" width="11.1640625" style="74"/>
+    <col min="14593" max="14593" width="3.83203125" style="74" customWidth="1"/>
+    <col min="14594" max="14594" width="5.83203125" style="74" customWidth="1"/>
+    <col min="14595" max="14595" width="8.83203125" style="74" customWidth="1"/>
     <col min="14596" max="14596" width="26" style="74" customWidth="1"/>
     <col min="14597" max="14597" width="12.5" style="74" customWidth="1"/>
-    <col min="14598" max="14598" width="7.296875" style="74" customWidth="1"/>
-    <col min="14599" max="14599" width="13.296875" style="74" customWidth="1"/>
-    <col min="14600" max="14600" width="12.296875" style="74" customWidth="1"/>
+    <col min="14598" max="14598" width="7.33203125" style="74" customWidth="1"/>
+    <col min="14599" max="14599" width="13.33203125" style="74" customWidth="1"/>
+    <col min="14600" max="14600" width="12.33203125" style="74" customWidth="1"/>
     <col min="14601" max="14601" width="15.5" style="74" customWidth="1"/>
-    <col min="14602" max="14602" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="14603" max="14603" width="11.19921875" style="74"/>
+    <col min="14602" max="14602" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="14603" max="14603" width="11.1640625" style="74"/>
     <col min="14604" max="14604" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="14605" max="14605" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="14606" max="14848" width="11.19921875" style="74"/>
-    <col min="14849" max="14849" width="3.796875" style="74" customWidth="1"/>
-    <col min="14850" max="14850" width="5.796875" style="74" customWidth="1"/>
-    <col min="14851" max="14851" width="8.796875" style="74" customWidth="1"/>
+    <col min="14605" max="14605" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="14606" max="14848" width="11.1640625" style="74"/>
+    <col min="14849" max="14849" width="3.83203125" style="74" customWidth="1"/>
+    <col min="14850" max="14850" width="5.83203125" style="74" customWidth="1"/>
+    <col min="14851" max="14851" width="8.83203125" style="74" customWidth="1"/>
     <col min="14852" max="14852" width="26" style="74" customWidth="1"/>
     <col min="14853" max="14853" width="12.5" style="74" customWidth="1"/>
-    <col min="14854" max="14854" width="7.296875" style="74" customWidth="1"/>
-    <col min="14855" max="14855" width="13.296875" style="74" customWidth="1"/>
-    <col min="14856" max="14856" width="12.296875" style="74" customWidth="1"/>
+    <col min="14854" max="14854" width="7.33203125" style="74" customWidth="1"/>
+    <col min="14855" max="14855" width="13.33203125" style="74" customWidth="1"/>
+    <col min="14856" max="14856" width="12.33203125" style="74" customWidth="1"/>
     <col min="14857" max="14857" width="15.5" style="74" customWidth="1"/>
-    <col min="14858" max="14858" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="14859" max="14859" width="11.19921875" style="74"/>
+    <col min="14858" max="14858" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="14859" max="14859" width="11.1640625" style="74"/>
     <col min="14860" max="14860" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="14861" max="14861" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="14862" max="15104" width="11.19921875" style="74"/>
-    <col min="15105" max="15105" width="3.796875" style="74" customWidth="1"/>
-    <col min="15106" max="15106" width="5.796875" style="74" customWidth="1"/>
-    <col min="15107" max="15107" width="8.796875" style="74" customWidth="1"/>
+    <col min="14861" max="14861" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="14862" max="15104" width="11.1640625" style="74"/>
+    <col min="15105" max="15105" width="3.83203125" style="74" customWidth="1"/>
+    <col min="15106" max="15106" width="5.83203125" style="74" customWidth="1"/>
+    <col min="15107" max="15107" width="8.83203125" style="74" customWidth="1"/>
     <col min="15108" max="15108" width="26" style="74" customWidth="1"/>
     <col min="15109" max="15109" width="12.5" style="74" customWidth="1"/>
-    <col min="15110" max="15110" width="7.296875" style="74" customWidth="1"/>
-    <col min="15111" max="15111" width="13.296875" style="74" customWidth="1"/>
-    <col min="15112" max="15112" width="12.296875" style="74" customWidth="1"/>
+    <col min="15110" max="15110" width="7.33203125" style="74" customWidth="1"/>
+    <col min="15111" max="15111" width="13.33203125" style="74" customWidth="1"/>
+    <col min="15112" max="15112" width="12.33203125" style="74" customWidth="1"/>
     <col min="15113" max="15113" width="15.5" style="74" customWidth="1"/>
-    <col min="15114" max="15114" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="15115" max="15115" width="11.19921875" style="74"/>
+    <col min="15114" max="15114" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="15115" max="15115" width="11.1640625" style="74"/>
     <col min="15116" max="15116" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="15117" max="15117" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="15118" max="15360" width="11.19921875" style="74"/>
-    <col min="15361" max="15361" width="3.796875" style="74" customWidth="1"/>
-    <col min="15362" max="15362" width="5.796875" style="74" customWidth="1"/>
-    <col min="15363" max="15363" width="8.796875" style="74" customWidth="1"/>
+    <col min="15117" max="15117" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="15118" max="15360" width="11.1640625" style="74"/>
+    <col min="15361" max="15361" width="3.83203125" style="74" customWidth="1"/>
+    <col min="15362" max="15362" width="5.83203125" style="74" customWidth="1"/>
+    <col min="15363" max="15363" width="8.83203125" style="74" customWidth="1"/>
     <col min="15364" max="15364" width="26" style="74" customWidth="1"/>
     <col min="15365" max="15365" width="12.5" style="74" customWidth="1"/>
-    <col min="15366" max="15366" width="7.296875" style="74" customWidth="1"/>
-    <col min="15367" max="15367" width="13.296875" style="74" customWidth="1"/>
-    <col min="15368" max="15368" width="12.296875" style="74" customWidth="1"/>
+    <col min="15366" max="15366" width="7.33203125" style="74" customWidth="1"/>
+    <col min="15367" max="15367" width="13.33203125" style="74" customWidth="1"/>
+    <col min="15368" max="15368" width="12.33203125" style="74" customWidth="1"/>
     <col min="15369" max="15369" width="15.5" style="74" customWidth="1"/>
-    <col min="15370" max="15370" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="15371" max="15371" width="11.19921875" style="74"/>
+    <col min="15370" max="15370" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="15371" max="15371" width="11.1640625" style="74"/>
     <col min="15372" max="15372" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="15373" max="15373" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="15374" max="15616" width="11.19921875" style="74"/>
-    <col min="15617" max="15617" width="3.796875" style="74" customWidth="1"/>
-    <col min="15618" max="15618" width="5.796875" style="74" customWidth="1"/>
-    <col min="15619" max="15619" width="8.796875" style="74" customWidth="1"/>
+    <col min="15373" max="15373" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="15374" max="15616" width="11.1640625" style="74"/>
+    <col min="15617" max="15617" width="3.83203125" style="74" customWidth="1"/>
+    <col min="15618" max="15618" width="5.83203125" style="74" customWidth="1"/>
+    <col min="15619" max="15619" width="8.83203125" style="74" customWidth="1"/>
     <col min="15620" max="15620" width="26" style="74" customWidth="1"/>
     <col min="15621" max="15621" width="12.5" style="74" customWidth="1"/>
-    <col min="15622" max="15622" width="7.296875" style="74" customWidth="1"/>
-    <col min="15623" max="15623" width="13.296875" style="74" customWidth="1"/>
-    <col min="15624" max="15624" width="12.296875" style="74" customWidth="1"/>
+    <col min="15622" max="15622" width="7.33203125" style="74" customWidth="1"/>
+    <col min="15623" max="15623" width="13.33203125" style="74" customWidth="1"/>
+    <col min="15624" max="15624" width="12.33203125" style="74" customWidth="1"/>
     <col min="15625" max="15625" width="15.5" style="74" customWidth="1"/>
-    <col min="15626" max="15626" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="15627" max="15627" width="11.19921875" style="74"/>
+    <col min="15626" max="15626" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="15627" max="15627" width="11.1640625" style="74"/>
     <col min="15628" max="15628" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="15629" max="15629" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="15630" max="15872" width="11.19921875" style="74"/>
-    <col min="15873" max="15873" width="3.796875" style="74" customWidth="1"/>
-    <col min="15874" max="15874" width="5.796875" style="74" customWidth="1"/>
-    <col min="15875" max="15875" width="8.796875" style="74" customWidth="1"/>
+    <col min="15629" max="15629" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="15630" max="15872" width="11.1640625" style="74"/>
+    <col min="15873" max="15873" width="3.83203125" style="74" customWidth="1"/>
+    <col min="15874" max="15874" width="5.83203125" style="74" customWidth="1"/>
+    <col min="15875" max="15875" width="8.83203125" style="74" customWidth="1"/>
     <col min="15876" max="15876" width="26" style="74" customWidth="1"/>
     <col min="15877" max="15877" width="12.5" style="74" customWidth="1"/>
-    <col min="15878" max="15878" width="7.296875" style="74" customWidth="1"/>
-    <col min="15879" max="15879" width="13.296875" style="74" customWidth="1"/>
-    <col min="15880" max="15880" width="12.296875" style="74" customWidth="1"/>
+    <col min="15878" max="15878" width="7.33203125" style="74" customWidth="1"/>
+    <col min="15879" max="15879" width="13.33203125" style="74" customWidth="1"/>
+    <col min="15880" max="15880" width="12.33203125" style="74" customWidth="1"/>
     <col min="15881" max="15881" width="15.5" style="74" customWidth="1"/>
-    <col min="15882" max="15882" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="15883" max="15883" width="11.19921875" style="74"/>
+    <col min="15882" max="15882" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="15883" max="15883" width="11.1640625" style="74"/>
     <col min="15884" max="15884" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="15885" max="15885" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="15886" max="16128" width="11.19921875" style="74"/>
-    <col min="16129" max="16129" width="3.796875" style="74" customWidth="1"/>
-    <col min="16130" max="16130" width="5.796875" style="74" customWidth="1"/>
-    <col min="16131" max="16131" width="8.796875" style="74" customWidth="1"/>
+    <col min="15885" max="15885" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="15886" max="16128" width="11.1640625" style="74"/>
+    <col min="16129" max="16129" width="3.83203125" style="74" customWidth="1"/>
+    <col min="16130" max="16130" width="5.83203125" style="74" customWidth="1"/>
+    <col min="16131" max="16131" width="8.83203125" style="74" customWidth="1"/>
     <col min="16132" max="16132" width="26" style="74" customWidth="1"/>
     <col min="16133" max="16133" width="12.5" style="74" customWidth="1"/>
-    <col min="16134" max="16134" width="7.296875" style="74" customWidth="1"/>
-    <col min="16135" max="16135" width="13.296875" style="74" customWidth="1"/>
-    <col min="16136" max="16136" width="12.296875" style="74" customWidth="1"/>
+    <col min="16134" max="16134" width="7.33203125" style="74" customWidth="1"/>
+    <col min="16135" max="16135" width="13.33203125" style="74" customWidth="1"/>
+    <col min="16136" max="16136" width="12.33203125" style="74" customWidth="1"/>
     <col min="16137" max="16137" width="15.5" style="74" customWidth="1"/>
-    <col min="16138" max="16138" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="16139" max="16139" width="11.19921875" style="74"/>
+    <col min="16138" max="16138" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="16139" max="16139" width="11.1640625" style="74"/>
     <col min="16140" max="16140" width="11.5" style="74" bestFit="1" customWidth="1"/>
-    <col min="16141" max="16141" width="11.296875" style="74" bestFit="1" customWidth="1"/>
-    <col min="16142" max="16384" width="11.19921875" style="74"/>
+    <col min="16141" max="16141" width="11.33203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="16142" max="16384" width="11.1640625" style="74"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" s="2" customFormat="1" ht="33.75" customHeight="1" thickBot="1">
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -4288,16 +4288,16 @@
       <c r="R1" s="3"/>
     </row>
     <row r="2" spans="2:18" s="2" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="135"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="106"/>
       <c r="M2" s="4" t="s">
         <v>60</v>
       </c>
@@ -4307,11 +4307,11 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="2:18" s="2" customFormat="1" ht="19.95" customHeight="1">
-      <c r="B3" s="136" t="s">
+    <row r="3" spans="2:18" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="B3" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="136"/>
+      <c r="C3" s="107"/>
       <c r="D3" s="5" t="s">
         <v>63</v>
       </c>
@@ -4330,11 +4330,11 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="2:18" s="2" customFormat="1" ht="19.95" customHeight="1">
-      <c r="B4" s="109" t="s">
+    <row r="4" spans="2:18" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="B4" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="109"/>
+      <c r="C4" s="102"/>
       <c r="D4" s="5" t="s">
         <v>58</v>
       </c>
@@ -4353,11 +4353,11 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="2:18" s="2" customFormat="1" ht="19.95" customHeight="1">
-      <c r="B5" s="109" t="s">
+    <row r="5" spans="2:18" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="B5" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="109"/>
+      <c r="C5" s="102"/>
       <c r="D5" s="5"/>
       <c r="E5" s="14"/>
       <c r="F5" s="10"/>
@@ -4374,11 +4374,11 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="2:18" s="2" customFormat="1" ht="19.95" customHeight="1">
-      <c r="B6" s="109" t="s">
+    <row r="6" spans="2:18" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="B6" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="109"/>
+      <c r="C6" s="102"/>
       <c r="D6" s="14">
         <v>46063</v>
       </c>
@@ -4397,11 +4397,11 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="2:18" s="2" customFormat="1" ht="19.95" customHeight="1">
-      <c r="B7" s="109" t="s">
+    <row r="7" spans="2:18" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="B7" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
+      <c r="C7" s="102"/>
       <c r="D7" s="15" t="s">
         <v>16</v>
       </c>
@@ -4420,11 +4420,11 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="2:18" s="2" customFormat="1" ht="19.95" customHeight="1">
-      <c r="B8" s="110" t="s">
+    <row r="8" spans="2:18" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="B8" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="110"/>
+      <c r="C8" s="108"/>
       <c r="D8" s="18" t="s">
         <v>20</v>
       </c>
@@ -4521,11 +4521,11 @@
       <c r="B12" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="111" t="s">
+      <c r="C12" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="112"/>
-      <c r="E12" s="113"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="111"/>
       <c r="F12" s="86" t="s">
         <v>25</v>
       </c>
@@ -4548,17 +4548,17 @@
       <c r="O12" s="39"/>
       <c r="P12" s="39"/>
     </row>
-    <row r="13" spans="2:18" s="44" customFormat="1" ht="16.95" customHeight="1">
-      <c r="B13" s="114" t="s">
+    <row r="13" spans="2:18" s="44" customFormat="1" ht="17" customHeight="1">
+      <c r="B13" s="112" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="118"/>
+      <c r="E13" s="116"/>
       <c r="F13" s="41" t="s">
         <v>32</v>
       </c>
@@ -4578,24 +4578,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:18" s="44" customFormat="1" ht="19.8" customHeight="1">
-      <c r="B14" s="115"/>
+    <row r="14" spans="2:18" s="44" customFormat="1" ht="19.75" customHeight="1">
+      <c r="B14" s="113"/>
       <c r="C14" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="119" t="s">
+      <c r="D14" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="120"/>
+      <c r="E14" s="118"/>
       <c r="F14" s="46"/>
-      <c r="G14" s="129">
+      <c r="G14" s="127">
         <v>13500000</v>
       </c>
       <c r="H14" s="42">
         <f>F14*G14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="97">
+      <c r="I14" s="136">
         <f>12000000*F18</f>
         <v>6000000</v>
       </c>
@@ -4606,22 +4606,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:18" s="44" customFormat="1" ht="19.8" customHeight="1">
-      <c r="B15" s="115"/>
+    <row r="15" spans="2:18" s="44" customFormat="1" ht="19.75" customHeight="1">
+      <c r="B15" s="113"/>
       <c r="C15" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="119" t="s">
+      <c r="D15" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="120"/>
+      <c r="E15" s="118"/>
       <c r="F15" s="46"/>
-      <c r="G15" s="130"/>
+      <c r="G15" s="128"/>
       <c r="H15" s="42">
         <f>G14*F15</f>
         <v>0</v>
       </c>
-      <c r="I15" s="98"/>
+      <c r="I15" s="137"/>
       <c r="L15" s="44" t="s">
         <v>57</v>
       </c>
@@ -4629,53 +4629,53 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:18" s="44" customFormat="1" ht="19.8" customHeight="1">
-      <c r="B16" s="115"/>
+    <row r="16" spans="2:18" s="44" customFormat="1" ht="19.75" customHeight="1">
+      <c r="B16" s="113"/>
       <c r="C16" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="121" t="s">
+      <c r="D16" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="122"/>
+      <c r="E16" s="120"/>
       <c r="F16" s="46">
         <v>0.5</v>
       </c>
-      <c r="G16" s="130"/>
+      <c r="G16" s="128"/>
       <c r="H16" s="42">
-        <f>ROUNDDOWN(G14*F16,-3)</f>
-        <v>6750000</v>
-      </c>
-      <c r="I16" s="98"/>
+        <f>G15*F16</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="137"/>
       <c r="M16" s="44">
         <f>SUM(M9:M15)</f>
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="44" customFormat="1" ht="19.8" customHeight="1" thickBot="1">
-      <c r="B17" s="115"/>
+    <row r="17" spans="1:13" s="44" customFormat="1" ht="19.75" customHeight="1" thickBot="1">
+      <c r="B17" s="113"/>
       <c r="C17" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="119" t="s">
+      <c r="D17" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="120"/>
+      <c r="E17" s="118"/>
       <c r="F17" s="46"/>
-      <c r="G17" s="131"/>
+      <c r="G17" s="129"/>
       <c r="H17" s="42">
         <f>G14*F17</f>
         <v>0</v>
       </c>
-      <c r="I17" s="98"/>
-    </row>
-    <row r="18" spans="1:13" s="44" customFormat="1" ht="16.95" customHeight="1">
-      <c r="B18" s="115"/>
-      <c r="C18" s="123" t="s">
+      <c r="I17" s="137"/>
+    </row>
+    <row r="18" spans="1:13" s="44" customFormat="1" ht="17" customHeight="1">
+      <c r="B18" s="113"/>
+      <c r="C18" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="124"/>
-      <c r="E18" s="125"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="123"/>
       <c r="F18" s="47">
         <f>SUM(F13:F17)</f>
         <v>0.5</v>
@@ -4686,23 +4686,23 @@
       </c>
       <c r="H18" s="48">
         <f>SUM(H13:H17)</f>
-        <v>6750000</v>
-      </c>
-      <c r="I18" s="99"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="138"/>
       <c r="J18" s="49" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="44" customFormat="1" ht="16.95" customHeight="1" thickBot="1">
-      <c r="B19" s="116"/>
-      <c r="C19" s="126" t="s">
+    <row r="19" spans="1:13" s="44" customFormat="1" ht="17" customHeight="1" thickBot="1">
+      <c r="B19" s="114"/>
+      <c r="C19" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="127"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="128"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="126"/>
       <c r="I19" s="90">
         <f>SUM(I13:I18)</f>
         <v>6000000</v>
@@ -4711,7 +4711,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="58" customFormat="1" ht="16.95" customHeight="1">
+    <row r="20" spans="1:13" s="58" customFormat="1" ht="17" customHeight="1">
       <c r="A20" s="51"/>
       <c r="B20" s="52"/>
       <c r="C20" s="53"/>
@@ -4725,13 +4725,13 @@
     <row r="21" spans="1:13" s="58" customFormat="1" ht="18" hidden="1" customHeight="1">
       <c r="A21" s="51"/>
       <c r="B21" s="59"/>
-      <c r="C21" s="100" t="s">
+      <c r="C21" s="139" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="103" t="s">
+      <c r="D21" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="104"/>
+      <c r="E21" s="143"/>
       <c r="F21" s="60" t="s">
         <v>46</v>
       </c>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="I21" s="63"/>
     </row>
-    <row r="22" spans="1:13" s="58" customFormat="1" ht="16.95" hidden="1" customHeight="1">
+    <row r="22" spans="1:13" s="58" customFormat="1" ht="17" hidden="1" customHeight="1">
       <c r="A22" s="51"/>
       <c r="B22" s="59"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="105" t="s">
+      <c r="C22" s="140"/>
+      <c r="D22" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="106"/>
+      <c r="E22" s="145"/>
       <c r="F22" s="64">
         <v>782099993</v>
       </c>
@@ -4767,9 +4767,9 @@
     <row r="23" spans="1:13" s="58" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="A23" s="51"/>
       <c r="B23" s="59"/>
-      <c r="C23" s="102"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="108"/>
+      <c r="C23" s="141"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="147"/>
       <c r="F23" s="67"/>
       <c r="G23" s="68">
         <f>F23*15%</f>
@@ -4778,7 +4778,7 @@
       <c r="H23" s="69"/>
       <c r="I23" s="63"/>
     </row>
-    <row r="24" spans="1:13" s="58" customFormat="1" ht="16.95" customHeight="1">
+    <row r="24" spans="1:13" s="58" customFormat="1" ht="17" customHeight="1">
       <c r="A24" s="51"/>
       <c r="B24" s="59"/>
       <c r="D24" s="70"/>
@@ -4790,16 +4790,16 @@
     </row>
     <row r="25" spans="1:13" s="78" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
       <c r="A25" s="74"/>
-      <c r="B25" s="91" t="str">
+      <c r="B25" s="130" t="str">
         <f>"제  안  금  액  합  계"&amp;IF(J11=0," (V.A.T 별도)"," (V.A.T 포함)")</f>
         <v>제  안  금  액  합  계 (V.A.T 별도)</v>
       </c>
-      <c r="C25" s="92"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="92"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="93"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="132"/>
       <c r="I25" s="75">
         <f>I19</f>
         <v>6000000</v>
@@ -4809,7 +4809,7 @@
       <c r="L25" s="77"/>
       <c r="M25" s="76"/>
     </row>
-    <row r="26" spans="1:13" s="78" customFormat="1" ht="16.2" thickBot="1">
+    <row r="26" spans="1:13" s="78" customFormat="1" ht="16" thickBot="1">
       <c r="A26" s="74"/>
       <c r="B26" s="79"/>
       <c r="C26" s="80"/>
@@ -4826,20 +4826,20 @@
       <c r="L26" s="74"/>
       <c r="M26" s="74"/>
     </row>
-    <row r="27" spans="1:13" s="78" customFormat="1" ht="80.55" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" s="78" customFormat="1" ht="80.5" customHeight="1" thickBot="1">
       <c r="A27" s="74"/>
       <c r="B27" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="94" t="s">
+      <c r="C27" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="95"/>
-      <c r="G27" s="95"/>
-      <c r="H27" s="95"/>
-      <c r="I27" s="96"/>
+      <c r="D27" s="134"/>
+      <c r="E27" s="134"/>
+      <c r="F27" s="134"/>
+      <c r="G27" s="134"/>
+      <c r="H27" s="134"/>
+      <c r="I27" s="135"/>
       <c r="J27" s="74"/>
       <c r="K27" s="74"/>
       <c r="L27" s="74"/>
@@ -4863,12 +4863,13 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="25">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="I14:I18"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="C12:E12"/>
@@ -4881,13 +4882,12 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="G14:G17"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="I14:I18"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -4908,270 +4908,270 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.69921875" style="138"/>
-    <col min="2" max="2" width="12.296875" style="138" customWidth="1"/>
-    <col min="3" max="3" width="30.796875" style="147" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.69921875" style="147" customWidth="1"/>
-    <col min="5" max="5" width="56.296875" style="147" customWidth="1"/>
-    <col min="6" max="6" width="16.09765625" style="146" customWidth="1"/>
-    <col min="7" max="16384" width="8.69921875" style="138"/>
+    <col min="1" max="1" width="8.6640625" style="92"/>
+    <col min="2" max="2" width="12.33203125" style="92" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" style="101" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" style="101" customWidth="1"/>
+    <col min="5" max="5" width="56.33203125" style="101" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" style="100" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="92"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:6">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="137" t="s">
+      <c r="C3" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137" t="s">
+      <c r="D3" s="91"/>
+      <c r="E3" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="137" t="s">
+      <c r="F3" s="91" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="139">
+      <c r="A4" s="93">
         <v>1</v>
       </c>
-      <c r="B4" s="139"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="139"/>
-    </row>
-    <row r="5" spans="1:6" ht="60.6" customHeight="1">
-      <c r="A5" s="141">
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="93"/>
+    </row>
+    <row r="5" spans="1:6" ht="60.5" customHeight="1">
+      <c r="A5" s="95">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="141" t="s">
+      <c r="B5" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="C5" s="96" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="142"/>
-      <c r="E5" s="143" t="s">
+      <c r="D5" s="96"/>
+      <c r="E5" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="141">
+      <c r="F5" s="95">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="60.6" customHeight="1">
-      <c r="A6" s="141">
+    <row r="6" spans="1:6" ht="60.5" customHeight="1">
+      <c r="A6" s="95">
         <v>1.2</v>
       </c>
-      <c r="B6" s="141" t="s">
+      <c r="B6" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="142" t="s">
+      <c r="C6" s="96" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="142"/>
-      <c r="E6" s="143" t="s">
+      <c r="D6" s="96"/>
+      <c r="E6" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="141">
+      <c r="F6" s="95">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="145" customFormat="1" ht="70.95" customHeight="1">
-      <c r="A7" s="141">
+    <row r="7" spans="1:6" s="99" customFormat="1" ht="71" customHeight="1">
+      <c r="A7" s="95">
         <v>2.1</v>
       </c>
-      <c r="B7" s="144" t="s">
+      <c r="B7" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="142"/>
-      <c r="E7" s="143" t="s">
+      <c r="D7" s="96"/>
+      <c r="E7" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="141">
+      <c r="F7" s="95">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="146"/>
-      <c r="B8" s="146"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="100"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="146"/>
-      <c r="B9" s="146"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="100"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="146"/>
-      <c r="B10" s="146"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="100"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="146"/>
-      <c r="B11" s="146"/>
+      <c r="A11" s="100"/>
+      <c r="B11" s="100"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="146"/>
-      <c r="B12" s="146"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="100"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="146"/>
-      <c r="B13" s="146"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="100"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="146"/>
-      <c r="B14" s="146"/>
+      <c r="A14" s="100"/>
+      <c r="B14" s="100"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="146"/>
-      <c r="B15" s="146"/>
+      <c r="A15" s="100"/>
+      <c r="B15" s="100"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="146"/>
-      <c r="B16" s="146"/>
+      <c r="A16" s="100"/>
+      <c r="B16" s="100"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="146"/>
-      <c r="B17" s="146"/>
+      <c r="A17" s="100"/>
+      <c r="B17" s="100"/>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="100"/>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="146"/>
-      <c r="B19" s="146"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="100"/>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="146"/>
-      <c r="B20" s="146"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="100"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="146"/>
-      <c r="B21" s="146"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="100"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="146"/>
-      <c r="B22" s="146"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="100"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="146"/>
-      <c r="B23" s="146"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="100"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="146"/>
-      <c r="B24" s="146"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="100"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="146"/>
-      <c r="B25" s="146"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="100"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="146"/>
-      <c r="B26" s="146"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="100"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="146"/>
-      <c r="B27" s="146"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="100"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="146"/>
-      <c r="B28" s="146"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="100"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="146"/>
-      <c r="B29" s="146"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="100"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="146"/>
-      <c r="B30" s="146"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="100"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="146"/>
-      <c r="B31" s="146"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="100"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="146"/>
-      <c r="B32" s="146"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="100"/>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="146"/>
-      <c r="B33" s="146"/>
+      <c r="A33" s="100"/>
+      <c r="B33" s="100"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="146"/>
-      <c r="B34" s="146"/>
+      <c r="A34" s="100"/>
+      <c r="B34" s="100"/>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="146"/>
-      <c r="B35" s="146"/>
+      <c r="A35" s="100"/>
+      <c r="B35" s="100"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="146"/>
-      <c r="B36" s="146"/>
+      <c r="A36" s="100"/>
+      <c r="B36" s="100"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="146"/>
-      <c r="B37" s="146"/>
+      <c r="A37" s="100"/>
+      <c r="B37" s="100"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="146"/>
-      <c r="B38" s="146"/>
+      <c r="A38" s="100"/>
+      <c r="B38" s="100"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="146"/>
-      <c r="B39" s="146"/>
+      <c r="A39" s="100"/>
+      <c r="B39" s="100"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="146"/>
-      <c r="B40" s="146"/>
+      <c r="A40" s="100"/>
+      <c r="B40" s="100"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="146"/>
-      <c r="B41" s="146"/>
+      <c r="A41" s="100"/>
+      <c r="B41" s="100"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="146"/>
-      <c r="B42" s="146"/>
+      <c r="A42" s="100"/>
+      <c r="B42" s="100"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="146"/>
-      <c r="B43" s="146"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="100"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="146"/>
-      <c r="B44" s="146"/>
+      <c r="A44" s="100"/>
+      <c r="B44" s="100"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="146"/>
-      <c r="B45" s="146"/>
+      <c r="A45" s="100"/>
+      <c r="B45" s="100"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="146"/>
-      <c r="B46" s="146"/>
+      <c r="A46" s="100"/>
+      <c r="B46" s="100"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="146"/>
-      <c r="B47" s="146"/>
+      <c r="A47" s="100"/>
+      <c r="B47" s="100"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="146"/>
-      <c r="B48" s="146"/>
+      <c r="A48" s="100"/>
+      <c r="B48" s="100"/>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="146"/>
-      <c r="B49" s="146"/>
+      <c r="A49" s="100"/>
+      <c r="B49" s="100"/>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="146"/>
-      <c r="B50" s="146"/>
+      <c r="A50" s="100"/>
+      <c r="B50" s="100"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5183,13 +5183,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{381F72FC-D612-465C-9252-E2520BEC5019}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
-    <col min="2" max="2" width="43.296875" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="35.549999999999997" customHeight="1">
+    <row r="1" spans="1:2" ht="35.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -5204,15 +5204,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="e61592f5-add8-4be3-94b4-19cf7edb8853">
@@ -5221,6 +5212,15 @@
     <TaxCatchAll xmlns="4ad34cc6-def4-401d-ad2c-4bd32b00908b" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5437,14 +5437,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72A3544C-41FF-4D7F-B6B6-893FA52E638D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{111F65EF-A78F-47C5-A638-9A40916DEC2E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -5457,6 +5449,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="4ad34cc6-def4-401d-ad2c-4bd32b00908b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72A3544C-41FF-4D7F-B6B6-893FA52E638D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
